--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t>Medonho´s F.C.</t>
+  </si>
+  <si>
+    <t>NHU PORÃ SAF.</t>
   </si>
   <si>
     <t>Pepe Leal FC</t>
@@ -488,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -563,7 +566,7 @@
         <v>20</v>
       </c>
       <c r="B3">
-        <v>63.56</v>
+        <v>63.56005859375</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -571,7 +574,7 @@
         <v>21</v>
       </c>
       <c r="B4">
-        <v>47.86</v>
+        <v>47.860107421875</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -579,7 +582,7 @@
         <v>22</v>
       </c>
       <c r="B5">
-        <v>66.37</v>
+        <v>66.3701171875</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -587,7 +590,7 @@
         <v>23</v>
       </c>
       <c r="B6">
-        <v>83.2</v>
+        <v>83.2001953125</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -595,7 +598,7 @@
         <v>24</v>
       </c>
       <c r="B7">
-        <v>53.66</v>
+        <v>53.659912109375</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -603,7 +606,7 @@
         <v>25</v>
       </c>
       <c r="B8">
-        <v>71.95999999999999</v>
+        <v>71.9599609375</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -611,7 +614,7 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>56.05</v>
+        <v>56.050048828125</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -619,7 +622,7 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>61.56</v>
+        <v>61.56005859375</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -627,7 +630,7 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>54.05</v>
+        <v>54.050048828125</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -635,7 +638,7 @@
         <v>29</v>
       </c>
       <c r="B12">
-        <v>47.86</v>
+        <v>47.860107421875</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -643,7 +646,7 @@
         <v>30</v>
       </c>
       <c r="B13">
-        <v>55.66</v>
+        <v>55.659912109375</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -651,7 +654,7 @@
         <v>31</v>
       </c>
       <c r="B14">
-        <v>62.56</v>
+        <v>62.56005859375</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -659,23 +662,20 @@
         <v>32</v>
       </c>
       <c r="B15">
-        <v>55.66</v>
+        <v>55.659912109375</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B16">
-        <v>60.6</v>
-      </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B17">
-        <v>61.16</v>
+        <v>60.60009765625</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -683,7 +683,7 @@
         <v>35</v>
       </c>
       <c r="B18">
-        <v>67.16</v>
+        <v>61.159912109375</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -691,7 +691,7 @@
         <v>36</v>
       </c>
       <c r="B19">
-        <v>54.9</v>
+        <v>67.16015625</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -699,14 +699,22 @@
         <v>37</v>
       </c>
       <c r="B20">
-        <v>68.06</v>
+        <v>54.89990234375</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21">
+        <v>68.06005859375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
         <v>23</v>
       </c>
     </row>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -560,6 +560,9 @@
       <c r="B2">
         <v>64.5</v>
       </c>
+      <c r="C2">
+        <v>42.8</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -568,6 +571,9 @@
       <c r="B3">
         <v>63.56005859375</v>
       </c>
+      <c r="C3">
+        <v>82.5</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -576,6 +582,9 @@
       <c r="B4">
         <v>47.860107421875</v>
       </c>
+      <c r="C4">
+        <v>67.25</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -584,6 +593,9 @@
       <c r="B5">
         <v>66.3701171875</v>
       </c>
+      <c r="C5">
+        <v>28.7</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -592,6 +604,9 @@
       <c r="B6">
         <v>83.2001953125</v>
       </c>
+      <c r="C6">
+        <v>83.5</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -600,6 +615,9 @@
       <c r="B7">
         <v>53.659912109375</v>
       </c>
+      <c r="C7">
+        <v>49.8</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -608,6 +626,9 @@
       <c r="B8">
         <v>71.9599609375</v>
       </c>
+      <c r="C8">
+        <v>53.6</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -616,6 +637,9 @@
       <c r="B9">
         <v>56.050048828125</v>
       </c>
+      <c r="C9">
+        <v>57.25</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -624,6 +648,9 @@
       <c r="B10">
         <v>61.56005859375</v>
       </c>
+      <c r="C10">
+        <v>41.7</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -632,6 +659,9 @@
       <c r="B11">
         <v>54.050048828125</v>
       </c>
+      <c r="C11">
+        <v>51.15</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -640,6 +670,9 @@
       <c r="B12">
         <v>47.860107421875</v>
       </c>
+      <c r="C12">
+        <v>52.8</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -648,6 +681,9 @@
       <c r="B13">
         <v>55.659912109375</v>
       </c>
+      <c r="C13">
+        <v>38.9</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -656,6 +692,9 @@
       <c r="B14">
         <v>62.56005859375</v>
       </c>
+      <c r="C14">
+        <v>55.9</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -664,57 +703,81 @@
       <c r="B15">
         <v>55.659912109375</v>
       </c>
+      <c r="C15">
+        <v>18.8</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
+      <c r="C16">
+        <v>63.85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B17">
         <v>60.60009765625</v>
       </c>
-    </row>
-    <row r="18" spans="1:2">
+      <c r="C17">
+        <v>48.95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B18">
         <v>61.159912109375</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
+      <c r="C18">
+        <v>57.65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B19">
         <v>67.16015625</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
+      <c r="C19">
+        <v>62.35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B20">
         <v>54.89990234375</v>
       </c>
-    </row>
-    <row r="21" spans="1:2">
+      <c r="C20">
+        <v>47.35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B21">
         <v>68.06005859375</v>
       </c>
-    </row>
-    <row r="22" spans="1:2">
+      <c r="C21">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="s">
         <v>23</v>
       </c>
     </row>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -671,7 +671,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C12">
-        <v>52.8</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="13" spans="1:20">

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -561,7 +561,7 @@
         <v>64.5</v>
       </c>
       <c r="C2">
-        <v>42.8</v>
+        <v>61.71</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -572,7 +572,7 @@
         <v>63.56005859375</v>
       </c>
       <c r="C3">
-        <v>82.5</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -583,7 +583,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C4">
-        <v>67.25</v>
+        <v>71.55</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -594,7 +594,7 @@
         <v>66.3701171875</v>
       </c>
       <c r="C5">
-        <v>28.7</v>
+        <v>34.41</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -605,7 +605,7 @@
         <v>83.2001953125</v>
       </c>
       <c r="C6">
-        <v>83.5</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -616,7 +616,7 @@
         <v>53.659912109375</v>
       </c>
       <c r="C7">
-        <v>49.8</v>
+        <v>61.41</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -627,7 +627,7 @@
         <v>71.9599609375</v>
       </c>
       <c r="C8">
-        <v>53.6</v>
+        <v>58.41</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -638,7 +638,7 @@
         <v>56.050048828125</v>
       </c>
       <c r="C9">
-        <v>57.25</v>
+        <v>66.25</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -649,7 +649,7 @@
         <v>61.56005859375</v>
       </c>
       <c r="C10">
-        <v>41.7</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -660,7 +660,7 @@
         <v>54.050048828125</v>
       </c>
       <c r="C11">
-        <v>51.15</v>
+        <v>68.84999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -671,7 +671,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C12">
-        <v>56.2</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -682,7 +682,7 @@
         <v>55.659912109375</v>
       </c>
       <c r="C13">
-        <v>38.9</v>
+        <v>59.6</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -693,7 +693,7 @@
         <v>62.56005859375</v>
       </c>
       <c r="C14">
-        <v>55.9</v>
+        <v>74.01000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -704,7 +704,7 @@
         <v>55.659912109375</v>
       </c>
       <c r="C15">
-        <v>18.8</v>
+        <v>29.81</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -712,7 +712,7 @@
         <v>33</v>
       </c>
       <c r="C16">
-        <v>63.85</v>
+        <v>94.47</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -723,7 +723,7 @@
         <v>60.60009765625</v>
       </c>
       <c r="C17">
-        <v>48.95</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -734,7 +734,7 @@
         <v>61.159912109375</v>
       </c>
       <c r="C18">
-        <v>57.65</v>
+        <v>63.36</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -745,7 +745,7 @@
         <v>67.16015625</v>
       </c>
       <c r="C19">
-        <v>62.35</v>
+        <v>82.55</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -756,7 +756,7 @@
         <v>54.89990234375</v>
       </c>
       <c r="C20">
-        <v>47.35</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -767,7 +767,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="C21">
-        <v>41.7</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -778,7 +778,7 @@
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -561,7 +561,7 @@
         <v>64.5</v>
       </c>
       <c r="C2">
-        <v>61.71</v>
+        <v>75.68000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -572,7 +572,7 @@
         <v>63.56005859375</v>
       </c>
       <c r="C3">
-        <v>85.90000000000001</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -583,7 +583,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C4">
-        <v>71.55</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -594,7 +594,7 @@
         <v>66.3701171875</v>
       </c>
       <c r="C5">
-        <v>34.41</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -605,7 +605,7 @@
         <v>83.2001953125</v>
       </c>
       <c r="C6">
-        <v>86.90000000000001</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -616,7 +616,7 @@
         <v>53.659912109375</v>
       </c>
       <c r="C7">
-        <v>61.41</v>
+        <v>81.48</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -627,7 +627,7 @@
         <v>71.9599609375</v>
       </c>
       <c r="C8">
-        <v>58.41</v>
+        <v>66.68000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -638,7 +638,7 @@
         <v>56.050048828125</v>
       </c>
       <c r="C9">
-        <v>66.25</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -649,7 +649,7 @@
         <v>61.56005859375</v>
       </c>
       <c r="C10">
-        <v>50.81</v>
+        <v>83.48</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -660,7 +660,7 @@
         <v>54.050048828125</v>
       </c>
       <c r="C11">
-        <v>68.84999999999999</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -671,7 +671,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C12">
-        <v>61.91</v>
+        <v>72.18000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -682,7 +682,7 @@
         <v>55.659912109375</v>
       </c>
       <c r="C13">
-        <v>59.6</v>
+        <v>73.59999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -693,7 +693,7 @@
         <v>62.56005859375</v>
       </c>
       <c r="C14">
-        <v>74.01000000000001</v>
+        <v>96.48</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -704,7 +704,7 @@
         <v>55.659912109375</v>
       </c>
       <c r="C15">
-        <v>29.81</v>
+        <v>55.78</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -712,7 +712,7 @@
         <v>33</v>
       </c>
       <c r="C16">
-        <v>94.47</v>
+        <v>95.41</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -723,7 +723,7 @@
         <v>60.60009765625</v>
       </c>
       <c r="C17">
-        <v>74.16</v>
+        <v>75.88</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -734,7 +734,7 @@
         <v>61.159912109375</v>
       </c>
       <c r="C18">
-        <v>63.36</v>
+        <v>71.18000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -745,7 +745,7 @@
         <v>67.16015625</v>
       </c>
       <c r="C19">
-        <v>82.55</v>
+        <v>86.45</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -756,7 +756,7 @@
         <v>54.89990234375</v>
       </c>
       <c r="C20">
-        <v>51.65</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -767,7 +767,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="C21">
-        <v>59.81</v>
+        <v>82.18000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -778,7 +778,7 @@
         <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -561,7 +561,7 @@
         <v>64.5</v>
       </c>
       <c r="C2">
-        <v>75.68000000000001</v>
+        <v>75.68017578125</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -583,7 +583,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C4">
-        <v>90.59999999999999</v>
+        <v>90.60009765625</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -594,7 +594,7 @@
         <v>66.3701171875</v>
       </c>
       <c r="C5">
-        <v>44.68</v>
+        <v>44.679931640625</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -605,7 +605,7 @@
         <v>83.2001953125</v>
       </c>
       <c r="C6">
-        <v>98.7</v>
+        <v>98.7001953125</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -616,7 +616,7 @@
         <v>53.659912109375</v>
       </c>
       <c r="C7">
-        <v>81.48</v>
+        <v>81.47998046875</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -627,7 +627,7 @@
         <v>71.9599609375</v>
       </c>
       <c r="C8">
-        <v>66.68000000000001</v>
+        <v>66.68017578125</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -638,7 +638,7 @@
         <v>56.050048828125</v>
       </c>
       <c r="C9">
-        <v>70.3</v>
+        <v>70.43994140625</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -649,7 +649,7 @@
         <v>61.56005859375</v>
       </c>
       <c r="C10">
-        <v>83.48</v>
+        <v>83.47998046875</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -660,7 +660,7 @@
         <v>54.050048828125</v>
       </c>
       <c r="C11">
-        <v>85.7</v>
+        <v>85.7001953125</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -671,7 +671,7 @@
         <v>47.860107421875</v>
       </c>
       <c r="C12">
-        <v>72.18000000000001</v>
+        <v>72.18017578125</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -682,7 +682,7 @@
         <v>55.659912109375</v>
       </c>
       <c r="C13">
-        <v>73.59999999999999</v>
+        <v>73.60009765625</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -693,7 +693,7 @@
         <v>62.56005859375</v>
       </c>
       <c r="C14">
-        <v>96.48</v>
+        <v>96.47998046875</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -704,7 +704,7 @@
         <v>55.659912109375</v>
       </c>
       <c r="C15">
-        <v>55.78</v>
+        <v>55.780029296875</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -712,7 +712,7 @@
         <v>33</v>
       </c>
       <c r="C16">
-        <v>95.41</v>
+        <v>95.41015625</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -723,7 +723,7 @@
         <v>60.60009765625</v>
       </c>
       <c r="C17">
-        <v>75.88</v>
+        <v>75.8798828125</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -734,7 +734,7 @@
         <v>61.159912109375</v>
       </c>
       <c r="C18">
-        <v>71.18000000000001</v>
+        <v>71.18017578125</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -745,7 +745,7 @@
         <v>67.16015625</v>
       </c>
       <c r="C19">
-        <v>86.45</v>
+        <v>86.4501953125</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -756,7 +756,7 @@
         <v>54.89990234375</v>
       </c>
       <c r="C20">
-        <v>77.59999999999999</v>
+        <v>77.60009765625</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -767,7 +767,7 @@
         <v>68.06005859375</v>
       </c>
       <c r="C21">
-        <v>82.18000000000001</v>
+        <v>82.18017578125</v>
       </c>
     </row>
     <row r="22" spans="1:3">

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -563,6 +563,9 @@
       <c r="C2">
         <v>75.68017578125</v>
       </c>
+      <c r="D2">
+        <v>38.37</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -574,6 +577,9 @@
       <c r="C3">
         <v>100.5</v>
       </c>
+      <c r="D3">
+        <v>32.07</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -585,6 +591,9 @@
       <c r="C4">
         <v>90.60009765625</v>
       </c>
+      <c r="D4">
+        <v>31.67</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -596,6 +605,9 @@
       <c r="C5">
         <v>44.679931640625</v>
       </c>
+      <c r="D5">
+        <v>31.19</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -607,6 +619,9 @@
       <c r="C6">
         <v>98.7001953125</v>
       </c>
+      <c r="D6">
+        <v>31.8</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -618,6 +633,9 @@
       <c r="C7">
         <v>81.47998046875</v>
       </c>
+      <c r="D7">
+        <v>38.07</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -629,6 +647,9 @@
       <c r="C8">
         <v>66.68017578125</v>
       </c>
+      <c r="D8">
+        <v>17.3</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -640,6 +661,9 @@
       <c r="C9">
         <v>70.43994140625</v>
       </c>
+      <c r="D9">
+        <v>20.29</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -651,6 +675,9 @@
       <c r="C10">
         <v>83.47998046875</v>
       </c>
+      <c r="D10">
+        <v>45.77</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -662,6 +689,9 @@
       <c r="C11">
         <v>85.7001953125</v>
       </c>
+      <c r="D11">
+        <v>35.47</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -673,6 +703,9 @@
       <c r="C12">
         <v>72.18017578125</v>
       </c>
+      <c r="D12">
+        <v>62.8</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -684,6 +717,9 @@
       <c r="C13">
         <v>73.60009765625</v>
       </c>
+      <c r="D13">
+        <v>41.97</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -695,6 +731,9 @@
       <c r="C14">
         <v>96.47998046875</v>
       </c>
+      <c r="D14">
+        <v>53.77</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -706,6 +745,9 @@
       <c r="C15">
         <v>55.780029296875</v>
       </c>
+      <c r="D15">
+        <v>45.59</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -714,8 +756,11 @@
       <c r="C16">
         <v>95.41015625</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16">
+        <v>32.79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -725,8 +770,11 @@
       <c r="C17">
         <v>75.8798828125</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17">
+        <v>34.49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -736,8 +784,11 @@
       <c r="C18">
         <v>71.18017578125</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18">
+        <v>41.87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -747,8 +798,11 @@
       <c r="C19">
         <v>86.4501953125</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19">
+        <v>44.97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -758,8 +812,11 @@
       <c r="C20">
         <v>77.60009765625</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20">
+        <v>32.67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -769,8 +826,11 @@
       <c r="C21">
         <v>82.18017578125</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21">
+        <v>45.17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -779,6 +839,9 @@
       </c>
       <c r="C22" t="s">
         <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -564,7 +564,7 @@
         <v>75.68017578125</v>
       </c>
       <c r="D2">
-        <v>38.37</v>
+        <v>73.26000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -578,7 +578,7 @@
         <v>100.5</v>
       </c>
       <c r="D3">
-        <v>32.07</v>
+        <v>91.66</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -592,7 +592,7 @@
         <v>90.60009765625</v>
       </c>
       <c r="D4">
-        <v>31.67</v>
+        <v>83.76000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -606,7 +606,7 @@
         <v>44.679931640625</v>
       </c>
       <c r="D5">
-        <v>31.19</v>
+        <v>81.04000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -620,7 +620,7 @@
         <v>98.7001953125</v>
       </c>
       <c r="D6">
-        <v>31.8</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -634,7 +634,7 @@
         <v>81.47998046875</v>
       </c>
       <c r="D7">
-        <v>38.07</v>
+        <v>78.45999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -648,7 +648,7 @@
         <v>66.68017578125</v>
       </c>
       <c r="D8">
-        <v>17.3</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -662,7 +662,7 @@
         <v>70.43994140625</v>
       </c>
       <c r="D9">
-        <v>20.29</v>
+        <v>70.04000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -676,7 +676,7 @@
         <v>83.47998046875</v>
       </c>
       <c r="D10">
-        <v>45.77</v>
+        <v>90.45999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -690,7 +690,7 @@
         <v>85.7001953125</v>
       </c>
       <c r="D11">
-        <v>35.47</v>
+        <v>65.66</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -704,7 +704,7 @@
         <v>72.18017578125</v>
       </c>
       <c r="D12">
-        <v>62.8</v>
+        <v>97.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -718,7 +718,7 @@
         <v>73.60009765625</v>
       </c>
       <c r="D13">
-        <v>41.97</v>
+        <v>99.26000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -732,7 +732,7 @@
         <v>96.47998046875</v>
       </c>
       <c r="D14">
-        <v>53.77</v>
+        <v>87.45999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -746,7 +746,7 @@
         <v>55.780029296875</v>
       </c>
       <c r="D15">
-        <v>45.59</v>
+        <v>88.14</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -757,7 +757,7 @@
         <v>95.41015625</v>
       </c>
       <c r="D16">
-        <v>32.79</v>
+        <v>56.24</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -771,7 +771,7 @@
         <v>75.8798828125</v>
       </c>
       <c r="D17">
-        <v>34.49</v>
+        <v>87.39</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -785,7 +785,7 @@
         <v>71.18017578125</v>
       </c>
       <c r="D18">
-        <v>41.87</v>
+        <v>72.26000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -799,7 +799,7 @@
         <v>86.4501953125</v>
       </c>
       <c r="D19">
-        <v>44.97</v>
+        <v>63.56</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -813,7 +813,7 @@
         <v>77.60009765625</v>
       </c>
       <c r="D20">
-        <v>32.67</v>
+        <v>77.45999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -827,7 +827,7 @@
         <v>82.18017578125</v>
       </c>
       <c r="D21">
-        <v>45.17</v>
+        <v>105.76</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -841,7 +841,7 @@
         <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -564,7 +564,7 @@
         <v>75.68017578125</v>
       </c>
       <c r="D2">
-        <v>73.26000000000001</v>
+        <v>73.259765625</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -578,7 +578,7 @@
         <v>100.5</v>
       </c>
       <c r="D3">
-        <v>91.66</v>
+        <v>91.66015625</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -592,7 +592,7 @@
         <v>90.60009765625</v>
       </c>
       <c r="D4">
-        <v>83.76000000000001</v>
+        <v>84.56005859375</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -606,7 +606,7 @@
         <v>44.679931640625</v>
       </c>
       <c r="D5">
-        <v>81.04000000000001</v>
+        <v>79.740234375</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -620,7 +620,7 @@
         <v>98.7001953125</v>
       </c>
       <c r="D6">
-        <v>108.2</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -634,7 +634,7 @@
         <v>81.47998046875</v>
       </c>
       <c r="D7">
-        <v>78.45999999999999</v>
+        <v>79.259765625</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -648,7 +648,7 @@
         <v>66.68017578125</v>
       </c>
       <c r="D8">
-        <v>42.1</v>
+        <v>42.14990234375</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -662,7 +662,7 @@
         <v>70.43994140625</v>
       </c>
       <c r="D9">
-        <v>70.04000000000001</v>
+        <v>71.64013671875</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -676,7 +676,7 @@
         <v>83.47998046875</v>
       </c>
       <c r="D10">
-        <v>90.45999999999999</v>
+        <v>90.4599609375</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -690,7 +690,7 @@
         <v>85.7001953125</v>
       </c>
       <c r="D11">
-        <v>65.66</v>
+        <v>65.66015625</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -704,7 +704,7 @@
         <v>72.18017578125</v>
       </c>
       <c r="D12">
-        <v>97.40000000000001</v>
+        <v>97.39990234375</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -718,7 +718,7 @@
         <v>73.60009765625</v>
       </c>
       <c r="D13">
-        <v>99.26000000000001</v>
+        <v>100.06005859375</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -732,7 +732,7 @@
         <v>96.47998046875</v>
       </c>
       <c r="D14">
-        <v>87.45999999999999</v>
+        <v>87.4599609375</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -746,7 +746,7 @@
         <v>55.780029296875</v>
       </c>
       <c r="D15">
-        <v>88.14</v>
+        <v>88.93994140625</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -757,7 +757,7 @@
         <v>95.41015625</v>
       </c>
       <c r="D16">
-        <v>56.24</v>
+        <v>57.0400390625</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -771,7 +771,7 @@
         <v>75.8798828125</v>
       </c>
       <c r="D17">
-        <v>87.39</v>
+        <v>87.39013671875</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -785,7 +785,7 @@
         <v>71.18017578125</v>
       </c>
       <c r="D18">
-        <v>72.26000000000001</v>
+        <v>73.06005859375</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -799,7 +799,7 @@
         <v>86.4501953125</v>
       </c>
       <c r="D19">
-        <v>63.56</v>
+        <v>64.35986328125</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -813,7 +813,7 @@
         <v>77.60009765625</v>
       </c>
       <c r="D20">
-        <v>77.45999999999999</v>
+        <v>78.259765625</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -827,7 +827,7 @@
         <v>82.18017578125</v>
       </c>
       <c r="D21">
-        <v>105.76</v>
+        <v>105.759765625</v>
       </c>
     </row>
     <row r="22" spans="1:4">

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -566,6 +566,9 @@
       <c r="D2">
         <v>73.259765625</v>
       </c>
+      <c r="E2">
+        <v>40.15</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -580,6 +583,9 @@
       <c r="D3">
         <v>91.66015625</v>
       </c>
+      <c r="E3">
+        <v>40.05</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -594,6 +600,9 @@
       <c r="D4">
         <v>84.56005859375</v>
       </c>
+      <c r="E4">
+        <v>44.4</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -608,6 +617,9 @@
       <c r="D5">
         <v>79.740234375</v>
       </c>
+      <c r="E5">
+        <v>29.6</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -622,6 +634,9 @@
       <c r="D6">
         <v>109</v>
       </c>
+      <c r="E6">
+        <v>61.45</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -636,6 +651,9 @@
       <c r="D7">
         <v>79.259765625</v>
       </c>
+      <c r="E7">
+        <v>59.53</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -650,6 +668,9 @@
       <c r="D8">
         <v>42.14990234375</v>
       </c>
+      <c r="E8">
+        <v>32.1</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -664,6 +685,9 @@
       <c r="D9">
         <v>71.64013671875</v>
       </c>
+      <c r="E9">
+        <v>45.3</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -678,6 +702,9 @@
       <c r="D10">
         <v>90.4599609375</v>
       </c>
+      <c r="E10">
+        <v>50.87</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -692,6 +719,9 @@
       <c r="D11">
         <v>65.66015625</v>
       </c>
+      <c r="E11">
+        <v>39.35</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -706,6 +736,9 @@
       <c r="D12">
         <v>97.39990234375</v>
       </c>
+      <c r="E12">
+        <v>65.55</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -720,6 +753,9 @@
       <c r="D13">
         <v>100.06005859375</v>
       </c>
+      <c r="E13">
+        <v>40.7</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -734,6 +770,9 @@
       <c r="D14">
         <v>87.4599609375</v>
       </c>
+      <c r="E14">
+        <v>44.6</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -748,6 +787,9 @@
       <c r="D15">
         <v>88.93994140625</v>
       </c>
+      <c r="E15">
+        <v>56.8</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -759,8 +801,11 @@
       <c r="D16">
         <v>57.0400390625</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16">
+        <v>48.94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -773,8 +818,11 @@
       <c r="D17">
         <v>87.39013671875</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17">
+        <v>29.84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -787,8 +835,11 @@
       <c r="D18">
         <v>73.06005859375</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18">
+        <v>39.05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -801,8 +852,11 @@
       <c r="D19">
         <v>64.35986328125</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19">
+        <v>54.43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -815,8 +869,11 @@
       <c r="D20">
         <v>78.259765625</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -829,8 +886,11 @@
       <c r="D21">
         <v>105.759765625</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21">
+        <v>43.8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -842,6 +902,9 @@
       </c>
       <c r="D22" t="s">
         <v>23</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -567,7 +567,7 @@
         <v>73.259765625</v>
       </c>
       <c r="E2">
-        <v>40.15</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -584,7 +584,7 @@
         <v>91.66015625</v>
       </c>
       <c r="E3">
-        <v>40.05</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -601,7 +601,7 @@
         <v>84.56005859375</v>
       </c>
       <c r="E4">
-        <v>44.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -618,7 +618,7 @@
         <v>79.740234375</v>
       </c>
       <c r="E5">
-        <v>29.6</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -635,7 +635,7 @@
         <v>109</v>
       </c>
       <c r="E6">
-        <v>61.45</v>
+        <v>75.95999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -652,7 +652,7 @@
         <v>79.259765625</v>
       </c>
       <c r="E7">
-        <v>59.53</v>
+        <v>68.73</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -669,7 +669,7 @@
         <v>42.14990234375</v>
       </c>
       <c r="E8">
-        <v>32.1</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -686,7 +686,7 @@
         <v>71.64013671875</v>
       </c>
       <c r="E9">
-        <v>45.3</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -703,7 +703,7 @@
         <v>90.4599609375</v>
       </c>
       <c r="E10">
-        <v>50.87</v>
+        <v>56.68</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -720,7 +720,7 @@
         <v>65.66015625</v>
       </c>
       <c r="E11">
-        <v>39.35</v>
+        <v>47.9</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -737,7 +737,7 @@
         <v>97.39990234375</v>
       </c>
       <c r="E12">
-        <v>65.55</v>
+        <v>81.65000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -754,7 +754,7 @@
         <v>100.06005859375</v>
       </c>
       <c r="E13">
-        <v>40.7</v>
+        <v>43.55</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -771,7 +771,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="E14">
-        <v>44.6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -788,7 +788,7 @@
         <v>88.93994140625</v>
       </c>
       <c r="E15">
-        <v>56.8</v>
+        <v>59.41</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -802,7 +802,7 @@
         <v>57.0400390625</v>
       </c>
       <c r="E16">
-        <v>48.94</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -819,7 +819,7 @@
         <v>87.39013671875</v>
       </c>
       <c r="E17">
-        <v>29.84</v>
+        <v>37.16</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -836,7 +836,7 @@
         <v>73.06005859375</v>
       </c>
       <c r="E18">
-        <v>39.05</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -853,7 +853,7 @@
         <v>64.35986328125</v>
       </c>
       <c r="E19">
-        <v>54.43</v>
+        <v>61.13</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -870,7 +870,7 @@
         <v>78.259765625</v>
       </c>
       <c r="E20">
-        <v>41.7</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -887,7 +887,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E21">
-        <v>43.8</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="22" spans="1:5">

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -567,7 +567,7 @@
         <v>73.259765625</v>
       </c>
       <c r="E2">
-        <v>43</v>
+        <v>49.43</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -584,7 +584,7 @@
         <v>91.66015625</v>
       </c>
       <c r="E3">
-        <v>51.6</v>
+        <v>77.23</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -601,7 +601,7 @@
         <v>84.56005859375</v>
       </c>
       <c r="E4">
-        <v>47.5</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -618,7 +618,7 @@
         <v>79.740234375</v>
       </c>
       <c r="E5">
-        <v>44.35</v>
+        <v>61.35</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -635,7 +635,7 @@
         <v>109</v>
       </c>
       <c r="E6">
-        <v>75.95999999999999</v>
+        <v>121.76</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -652,7 +652,7 @@
         <v>79.259765625</v>
       </c>
       <c r="E7">
-        <v>68.73</v>
+        <v>86.43000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -686,7 +686,7 @@
         <v>71.64013671875</v>
       </c>
       <c r="E9">
-        <v>56.16</v>
+        <v>56.36</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -703,7 +703,7 @@
         <v>90.4599609375</v>
       </c>
       <c r="E10">
-        <v>56.68</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -720,7 +720,7 @@
         <v>65.66015625</v>
       </c>
       <c r="E11">
-        <v>47.9</v>
+        <v>49.45</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -754,7 +754,7 @@
         <v>100.06005859375</v>
       </c>
       <c r="E13">
-        <v>43.55</v>
+        <v>62.75</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -771,7 +771,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="E14">
-        <v>58</v>
+        <v>81.43000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -802,7 +802,7 @@
         <v>57.0400390625</v>
       </c>
       <c r="E16">
-        <v>47.84</v>
+        <v>72.23999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -819,7 +819,7 @@
         <v>87.39013671875</v>
       </c>
       <c r="E17">
-        <v>37.16</v>
+        <v>42.56</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -870,7 +870,7 @@
         <v>78.259765625</v>
       </c>
       <c r="E20">
-        <v>43.35</v>
+        <v>45.55</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -887,7 +887,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E21">
-        <v>46.65</v>
+        <v>65.15000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -904,7 +904,7 @@
         <v>23</v>
       </c>
       <c r="E22" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -567,7 +567,7 @@
         <v>73.259765625</v>
       </c>
       <c r="E2">
-        <v>49.43</v>
+        <v>49.429931640625</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -584,7 +584,7 @@
         <v>91.66015625</v>
       </c>
       <c r="E3">
-        <v>77.23</v>
+        <v>77.22998046875</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -618,7 +618,7 @@
         <v>79.740234375</v>
       </c>
       <c r="E5">
-        <v>61.35</v>
+        <v>61.35009765625</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -635,7 +635,7 @@
         <v>109</v>
       </c>
       <c r="E6">
-        <v>121.76</v>
+        <v>121.759765625</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -652,7 +652,7 @@
         <v>79.259765625</v>
       </c>
       <c r="E7">
-        <v>86.43000000000001</v>
+        <v>86.43017578125</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -669,7 +669,7 @@
         <v>42.14990234375</v>
       </c>
       <c r="E8">
-        <v>30.8</v>
+        <v>30.800048828125</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -686,7 +686,7 @@
         <v>71.64013671875</v>
       </c>
       <c r="E9">
-        <v>56.36</v>
+        <v>56.360107421875</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -703,7 +703,7 @@
         <v>90.4599609375</v>
       </c>
       <c r="E10">
-        <v>76.06</v>
+        <v>76.06005859375</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -720,7 +720,7 @@
         <v>65.66015625</v>
       </c>
       <c r="E11">
-        <v>49.45</v>
+        <v>49.449951171875</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -737,7 +737,7 @@
         <v>97.39990234375</v>
       </c>
       <c r="E12">
-        <v>81.65000000000001</v>
+        <v>81.64990234375</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -771,7 +771,7 @@
         <v>87.4599609375</v>
       </c>
       <c r="E14">
-        <v>81.43000000000001</v>
+        <v>81.43017578125</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -788,7 +788,7 @@
         <v>88.93994140625</v>
       </c>
       <c r="E15">
-        <v>59.41</v>
+        <v>59.409912109375</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -802,7 +802,7 @@
         <v>57.0400390625</v>
       </c>
       <c r="E16">
-        <v>72.23999999999999</v>
+        <v>72.240234375</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -819,7 +819,7 @@
         <v>87.39013671875</v>
       </c>
       <c r="E17">
-        <v>42.56</v>
+        <v>42.56005859375</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -836,7 +836,7 @@
         <v>73.06005859375</v>
       </c>
       <c r="E18">
-        <v>42.56</v>
+        <v>42.56005859375</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -853,7 +853,7 @@
         <v>64.35986328125</v>
       </c>
       <c r="E19">
-        <v>61.13</v>
+        <v>61.1298828125</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -870,7 +870,7 @@
         <v>78.259765625</v>
       </c>
       <c r="E20">
-        <v>45.55</v>
+        <v>45.550048828125</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -887,7 +887,7 @@
         <v>105.759765625</v>
       </c>
       <c r="E21">
-        <v>65.15000000000001</v>
+        <v>65.14990234375</v>
       </c>
     </row>
     <row r="22" spans="1:5">

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -92,9 +92,6 @@
   </si>
   <si>
     <t>GaúchoDaFronteira F.C</t>
-  </si>
-  <si>
-    <t>GE Bebum</t>
   </si>
   <si>
     <t>GrioTeam</t>
@@ -491,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -569,6 +566,9 @@
       <c r="E2">
         <v>49.429931640625</v>
       </c>
+      <c r="F2">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -586,6 +586,9 @@
       <c r="E3">
         <v>77.22998046875</v>
       </c>
+      <c r="F3">
+        <v>22.7</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -603,6 +606,9 @@
       <c r="E4">
         <v>55</v>
       </c>
+      <c r="F4">
+        <v>17.6</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -620,6 +626,9 @@
       <c r="E5">
         <v>61.35009765625</v>
       </c>
+      <c r="F5">
+        <v>15.2</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -637,6 +646,9 @@
       <c r="E6">
         <v>121.759765625</v>
       </c>
+      <c r="F6">
+        <v>27.6</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -654,6 +666,9 @@
       <c r="E7">
         <v>86.43017578125</v>
       </c>
+      <c r="F7">
+        <v>25.7</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -671,22 +686,28 @@
       <c r="E8">
         <v>30.800048828125</v>
       </c>
+      <c r="F8">
+        <v>39.15</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B9">
-        <v>56.050048828125</v>
+        <v>61.56005859375</v>
       </c>
       <c r="C9">
-        <v>70.43994140625</v>
+        <v>83.47998046875</v>
       </c>
       <c r="D9">
-        <v>71.64013671875</v>
+        <v>90.4599609375</v>
       </c>
       <c r="E9">
-        <v>56.360107421875</v>
+        <v>76.06005859375</v>
+      </c>
+      <c r="F9">
+        <v>2.2</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -694,16 +715,19 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>61.56005859375</v>
+        <v>54.050048828125</v>
       </c>
       <c r="C10">
-        <v>83.47998046875</v>
+        <v>85.7001953125</v>
       </c>
       <c r="D10">
-        <v>90.4599609375</v>
+        <v>65.66015625</v>
       </c>
       <c r="E10">
-        <v>76.06005859375</v>
+        <v>49.449951171875</v>
+      </c>
+      <c r="F10">
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -711,16 +735,19 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>54.050048828125</v>
+        <v>47.860107421875</v>
       </c>
       <c r="C11">
-        <v>85.7001953125</v>
+        <v>72.18017578125</v>
       </c>
       <c r="D11">
-        <v>65.66015625</v>
+        <v>97.39990234375</v>
       </c>
       <c r="E11">
-        <v>49.449951171875</v>
+        <v>81.64990234375</v>
+      </c>
+      <c r="F11">
+        <v>13.8</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -728,16 +755,19 @@
         <v>29</v>
       </c>
       <c r="B12">
-        <v>47.860107421875</v>
+        <v>55.659912109375</v>
       </c>
       <c r="C12">
-        <v>72.18017578125</v>
+        <v>73.60009765625</v>
       </c>
       <c r="D12">
-        <v>97.39990234375</v>
+        <v>100.06005859375</v>
       </c>
       <c r="E12">
-        <v>81.64990234375</v>
+        <v>62.75</v>
+      </c>
+      <c r="F12">
+        <v>6.7</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -745,16 +775,19 @@
         <v>30</v>
       </c>
       <c r="B13">
-        <v>55.659912109375</v>
+        <v>62.56005859375</v>
       </c>
       <c r="C13">
-        <v>73.60009765625</v>
+        <v>96.47998046875</v>
       </c>
       <c r="D13">
-        <v>100.06005859375</v>
+        <v>87.4599609375</v>
       </c>
       <c r="E13">
-        <v>62.75</v>
+        <v>81.43017578125</v>
+      </c>
+      <c r="F13">
+        <v>11.7</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -762,149 +795,156 @@
         <v>31</v>
       </c>
       <c r="B14">
-        <v>62.56005859375</v>
+        <v>55.659912109375</v>
       </c>
       <c r="C14">
-        <v>96.47998046875</v>
+        <v>55.780029296875</v>
       </c>
       <c r="D14">
-        <v>87.4599609375</v>
+        <v>88.93994140625</v>
       </c>
       <c r="E14">
-        <v>81.43017578125</v>
+        <v>59.409912109375</v>
+      </c>
+      <c r="F14">
+        <v>10.7</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B15">
-        <v>55.659912109375</v>
-      </c>
       <c r="C15">
-        <v>55.780029296875</v>
+        <v>95.41015625</v>
       </c>
       <c r="D15">
-        <v>88.93994140625</v>
+        <v>57.0400390625</v>
       </c>
       <c r="E15">
-        <v>59.409912109375</v>
+        <v>72.240234375</v>
+      </c>
+      <c r="F15">
+        <v>9.75</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="B16">
+        <v>60.60009765625</v>
+      </c>
       <c r="C16">
-        <v>95.41015625</v>
+        <v>75.8798828125</v>
       </c>
       <c r="D16">
-        <v>57.0400390625</v>
+        <v>87.39013671875</v>
       </c>
       <c r="E16">
-        <v>72.240234375</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>42.56005859375</v>
+      </c>
+      <c r="F16">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B17">
-        <v>60.60009765625</v>
+        <v>61.159912109375</v>
       </c>
       <c r="C17">
-        <v>75.8798828125</v>
+        <v>71.18017578125</v>
       </c>
       <c r="D17">
-        <v>87.39013671875</v>
+        <v>73.06005859375</v>
       </c>
       <c r="E17">
         <v>42.56005859375</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B18">
-        <v>61.159912109375</v>
+        <v>67.16015625</v>
       </c>
       <c r="C18">
-        <v>71.18017578125</v>
+        <v>86.4501953125</v>
       </c>
       <c r="D18">
-        <v>73.06005859375</v>
+        <v>64.35986328125</v>
       </c>
       <c r="E18">
-        <v>42.56005859375</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>61.1298828125</v>
+      </c>
+      <c r="F18">
+        <v>25.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B19">
-        <v>67.16015625</v>
+        <v>54.89990234375</v>
       </c>
       <c r="C19">
-        <v>86.4501953125</v>
+        <v>77.60009765625</v>
       </c>
       <c r="D19">
-        <v>64.35986328125</v>
+        <v>78.259765625</v>
       </c>
       <c r="E19">
-        <v>61.1298828125</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>45.550048828125</v>
+      </c>
+      <c r="F19">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B20">
-        <v>54.89990234375</v>
+        <v>68.06005859375</v>
       </c>
       <c r="C20">
-        <v>77.60009765625</v>
+        <v>82.18017578125</v>
       </c>
       <c r="D20">
-        <v>78.259765625</v>
+        <v>105.759765625</v>
       </c>
       <c r="E20">
-        <v>45.550048828125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>65.14990234375</v>
+      </c>
+      <c r="F20">
+        <v>22.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B21">
-        <v>68.06005859375</v>
-      </c>
-      <c r="C21">
-        <v>82.18017578125</v>
-      </c>
-      <c r="D21">
-        <v>105.759765625</v>
-      </c>
-      <c r="E21">
-        <v>65.14990234375</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="B21" t="s">
         <v>23</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C21" t="s">
         <v>20</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D21" t="s">
         <v>23</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E21" t="s">
         <v>23</v>
+      </c>
+      <c r="F21" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -567,7 +567,7 @@
         <v>49.429931640625</v>
       </c>
       <c r="F2">
-        <v>22.7</v>
+        <v>87.919921875</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -587,7 +587,7 @@
         <v>77.22998046875</v>
       </c>
       <c r="F3">
-        <v>22.7</v>
+        <v>78.47021484375</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -607,7 +607,7 @@
         <v>55</v>
       </c>
       <c r="F4">
-        <v>17.6</v>
+        <v>63.8701171875</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -627,7 +627,7 @@
         <v>61.35009765625</v>
       </c>
       <c r="F5">
-        <v>15.2</v>
+        <v>82.31982421875</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -647,7 +647,7 @@
         <v>121.759765625</v>
       </c>
       <c r="F6">
-        <v>27.6</v>
+        <v>93.06982421875</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -667,7 +667,7 @@
         <v>86.43017578125</v>
       </c>
       <c r="F7">
-        <v>25.7</v>
+        <v>86.419921875</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -687,7 +687,7 @@
         <v>30.800048828125</v>
       </c>
       <c r="F8">
-        <v>39.15</v>
+        <v>52.5400390625</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -707,7 +707,7 @@
         <v>76.06005859375</v>
       </c>
       <c r="F9">
-        <v>2.2</v>
+        <v>41.169921875</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -727,7 +727,7 @@
         <v>49.449951171875</v>
       </c>
       <c r="F10">
-        <v>22</v>
+        <v>87.72021484375</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -747,7 +747,7 @@
         <v>81.64990234375</v>
       </c>
       <c r="F11">
-        <v>13.8</v>
+        <v>84.81982421875</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -767,7 +767,7 @@
         <v>62.75</v>
       </c>
       <c r="F12">
-        <v>6.7</v>
+        <v>77.22021484375</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -787,7 +787,7 @@
         <v>81.43017578125</v>
       </c>
       <c r="F13">
-        <v>11.7</v>
+        <v>85.669921875</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -807,7 +807,7 @@
         <v>59.409912109375</v>
       </c>
       <c r="F14">
-        <v>10.7</v>
+        <v>84.6201171875</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -824,7 +824,7 @@
         <v>72.240234375</v>
       </c>
       <c r="F15">
-        <v>9.75</v>
+        <v>69.77001953125</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -844,7 +844,7 @@
         <v>42.56005859375</v>
       </c>
       <c r="F16">
-        <v>7.4</v>
+        <v>49.77001953125</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -864,7 +864,7 @@
         <v>42.56005859375</v>
       </c>
       <c r="F17">
-        <v>17.9</v>
+        <v>70.85986328125</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -884,7 +884,7 @@
         <v>61.1298828125</v>
       </c>
       <c r="F18">
-        <v>25.9</v>
+        <v>72.759765625</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -904,7 +904,7 @@
         <v>45.550048828125</v>
       </c>
       <c r="F19">
-        <v>17.9</v>
+        <v>77.6201171875</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -924,7 +924,7 @@
         <v>65.14990234375</v>
       </c>
       <c r="F20">
-        <v>22.3</v>
+        <v>93.02001953125</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -944,7 +944,7 @@
         <v>23</v>
       </c>
       <c r="F21" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>GaúchoDaFronteira F.C</t>
+  </si>
+  <si>
+    <t>GE Xavanchesteer</t>
   </si>
   <si>
     <t>GrioTeam</t>
@@ -488,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T21"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:20">
@@ -695,19 +698,19 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>61.56005859375</v>
+        <v>56.050048828125</v>
       </c>
       <c r="C9">
-        <v>83.47998046875</v>
+        <v>70.43994140625</v>
       </c>
       <c r="D9">
-        <v>90.4599609375</v>
+        <v>71.64013671875</v>
       </c>
       <c r="E9">
-        <v>76.06005859375</v>
+        <v>56.360107421875</v>
       </c>
       <c r="F9">
-        <v>41.169921875</v>
+        <v>88.240234375</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -715,19 +718,19 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>54.050048828125</v>
+        <v>61.56005859375</v>
       </c>
       <c r="C10">
-        <v>85.7001953125</v>
+        <v>83.47998046875</v>
       </c>
       <c r="D10">
-        <v>65.66015625</v>
+        <v>90.4599609375</v>
       </c>
       <c r="E10">
-        <v>49.449951171875</v>
+        <v>76.06005859375</v>
       </c>
       <c r="F10">
-        <v>87.72021484375</v>
+        <v>41.169921875</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -735,19 +738,19 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>47.860107421875</v>
+        <v>54.050048828125</v>
       </c>
       <c r="C11">
-        <v>72.18017578125</v>
+        <v>85.7001953125</v>
       </c>
       <c r="D11">
-        <v>97.39990234375</v>
+        <v>65.66015625</v>
       </c>
       <c r="E11">
-        <v>81.64990234375</v>
+        <v>49.449951171875</v>
       </c>
       <c r="F11">
-        <v>84.81982421875</v>
+        <v>87.72021484375</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -755,19 +758,19 @@
         <v>29</v>
       </c>
       <c r="B12">
-        <v>55.659912109375</v>
+        <v>47.860107421875</v>
       </c>
       <c r="C12">
-        <v>73.60009765625</v>
+        <v>72.18017578125</v>
       </c>
       <c r="D12">
-        <v>100.06005859375</v>
+        <v>97.39990234375</v>
       </c>
       <c r="E12">
-        <v>62.75</v>
+        <v>81.64990234375</v>
       </c>
       <c r="F12">
-        <v>77.22021484375</v>
+        <v>84.81982421875</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -775,19 +778,19 @@
         <v>30</v>
       </c>
       <c r="B13">
-        <v>62.56005859375</v>
+        <v>55.659912109375</v>
       </c>
       <c r="C13">
-        <v>96.47998046875</v>
+        <v>73.60009765625</v>
       </c>
       <c r="D13">
-        <v>87.4599609375</v>
+        <v>100.06005859375</v>
       </c>
       <c r="E13">
-        <v>81.43017578125</v>
+        <v>62.75</v>
       </c>
       <c r="F13">
-        <v>85.669921875</v>
+        <v>77.22021484375</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -795,56 +798,56 @@
         <v>31</v>
       </c>
       <c r="B14">
-        <v>55.659912109375</v>
+        <v>62.56005859375</v>
       </c>
       <c r="C14">
-        <v>55.780029296875</v>
+        <v>96.47998046875</v>
       </c>
       <c r="D14">
-        <v>88.93994140625</v>
+        <v>87.4599609375</v>
       </c>
       <c r="E14">
-        <v>59.409912109375</v>
+        <v>81.43017578125</v>
       </c>
       <c r="F14">
-        <v>84.6201171875</v>
+        <v>85.669921875</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="B15">
+        <v>55.659912109375</v>
+      </c>
       <c r="C15">
-        <v>95.41015625</v>
+        <v>55.780029296875</v>
       </c>
       <c r="D15">
-        <v>57.0400390625</v>
+        <v>88.93994140625</v>
       </c>
       <c r="E15">
-        <v>72.240234375</v>
+        <v>59.409912109375</v>
       </c>
       <c r="F15">
-        <v>69.77001953125</v>
+        <v>84.6201171875</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B16">
-        <v>60.60009765625</v>
-      </c>
       <c r="C16">
-        <v>75.8798828125</v>
+        <v>95.41015625</v>
       </c>
       <c r="D16">
-        <v>87.39013671875</v>
+        <v>57.0400390625</v>
       </c>
       <c r="E16">
-        <v>42.56005859375</v>
+        <v>72.240234375</v>
       </c>
       <c r="F16">
-        <v>49.77001953125</v>
+        <v>69.77001953125</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -852,19 +855,19 @@
         <v>34</v>
       </c>
       <c r="B17">
-        <v>61.159912109375</v>
+        <v>60.60009765625</v>
       </c>
       <c r="C17">
-        <v>71.18017578125</v>
+        <v>75.8798828125</v>
       </c>
       <c r="D17">
-        <v>73.06005859375</v>
+        <v>87.39013671875</v>
       </c>
       <c r="E17">
         <v>42.56005859375</v>
       </c>
       <c r="F17">
-        <v>70.85986328125</v>
+        <v>49.77001953125</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -872,19 +875,19 @@
         <v>35</v>
       </c>
       <c r="B18">
-        <v>67.16015625</v>
+        <v>61.159912109375</v>
       </c>
       <c r="C18">
-        <v>86.4501953125</v>
+        <v>71.18017578125</v>
       </c>
       <c r="D18">
-        <v>64.35986328125</v>
+        <v>73.06005859375</v>
       </c>
       <c r="E18">
-        <v>61.1298828125</v>
+        <v>42.56005859375</v>
       </c>
       <c r="F18">
-        <v>72.759765625</v>
+        <v>70.85986328125</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -892,19 +895,19 @@
         <v>36</v>
       </c>
       <c r="B19">
-        <v>54.89990234375</v>
+        <v>67.16015625</v>
       </c>
       <c r="C19">
-        <v>77.60009765625</v>
+        <v>86.4501953125</v>
       </c>
       <c r="D19">
-        <v>78.259765625</v>
+        <v>64.35986328125</v>
       </c>
       <c r="E19">
-        <v>45.550048828125</v>
+        <v>61.1298828125</v>
       </c>
       <c r="F19">
-        <v>77.6201171875</v>
+        <v>72.759765625</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -912,38 +915,58 @@
         <v>37</v>
       </c>
       <c r="B20">
-        <v>68.06005859375</v>
+        <v>54.89990234375</v>
       </c>
       <c r="C20">
-        <v>82.18017578125</v>
+        <v>77.60009765625</v>
       </c>
       <c r="D20">
-        <v>105.759765625</v>
+        <v>78.259765625</v>
       </c>
       <c r="E20">
-        <v>65.14990234375</v>
+        <v>45.550048828125</v>
       </c>
       <c r="F20">
-        <v>93.02001953125</v>
+        <v>77.6201171875</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21">
+        <v>68.06005859375</v>
+      </c>
+      <c r="C21">
+        <v>82.18017578125</v>
+      </c>
+      <c r="D21">
+        <v>105.759765625</v>
+      </c>
+      <c r="E21">
+        <v>65.14990234375</v>
+      </c>
+      <c r="F21">
+        <v>93.02001953125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
         <v>23</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>20</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D22" t="s">
         <v>23</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E22" t="s">
         <v>23</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F22" t="s">
         <v>23</v>
       </c>
     </row>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -572,6 +572,9 @@
       <c r="F2">
         <v>87.919921875</v>
       </c>
+      <c r="G2">
+        <v>63.21</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -592,6 +595,9 @@
       <c r="F3">
         <v>78.47021484375</v>
       </c>
+      <c r="G3">
+        <v>63.71</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -612,6 +618,9 @@
       <c r="F4">
         <v>63.8701171875</v>
       </c>
+      <c r="G4">
+        <v>64.81</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -632,6 +641,9 @@
       <c r="F5">
         <v>82.31982421875</v>
       </c>
+      <c r="G5">
+        <v>70.59999999999999</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -652,6 +664,9 @@
       <c r="F6">
         <v>93.06982421875</v>
       </c>
+      <c r="G6">
+        <v>75.36</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -672,6 +687,9 @@
       <c r="F7">
         <v>86.419921875</v>
       </c>
+      <c r="G7">
+        <v>47.39</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -692,6 +710,9 @@
       <c r="F8">
         <v>52.5400390625</v>
       </c>
+      <c r="G8">
+        <v>34.55</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -712,6 +733,9 @@
       <c r="F9">
         <v>88.240234375</v>
       </c>
+      <c r="G9">
+        <v>61.99</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -732,6 +756,9 @@
       <c r="F10">
         <v>41.169921875</v>
       </c>
+      <c r="G10">
+        <v>71.01000000000001</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -752,6 +779,9 @@
       <c r="F11">
         <v>87.72021484375</v>
       </c>
+      <c r="G11">
+        <v>77.8</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -772,6 +802,9 @@
       <c r="F12">
         <v>84.81982421875</v>
       </c>
+      <c r="G12">
+        <v>62.01</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -792,6 +825,9 @@
       <c r="F13">
         <v>77.22021484375</v>
       </c>
+      <c r="G13">
+        <v>88.20999999999999</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -812,6 +848,9 @@
       <c r="F14">
         <v>85.669921875</v>
       </c>
+      <c r="G14">
+        <v>58.61</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -832,6 +871,9 @@
       <c r="F15">
         <v>84.6201171875</v>
       </c>
+      <c r="G15">
+        <v>75.81</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -849,8 +891,11 @@
       <c r="F16">
         <v>69.77001953125</v>
       </c>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16">
+        <v>47.99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -869,8 +914,11 @@
       <c r="F17">
         <v>49.77001953125</v>
       </c>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17">
+        <v>55.38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -889,8 +937,11 @@
       <c r="F18">
         <v>70.85986328125</v>
       </c>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18">
+        <v>67.59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -909,8 +960,11 @@
       <c r="F19">
         <v>72.759765625</v>
       </c>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19">
+        <v>61.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -929,8 +983,11 @@
       <c r="F20">
         <v>77.6201171875</v>
       </c>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20">
+        <v>79.01000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -949,8 +1006,11 @@
       <c r="F21">
         <v>93.02001953125</v>
       </c>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -968,6 +1028,9 @@
       </c>
       <c r="F22" t="s">
         <v>23</v>
+      </c>
+      <c r="G22" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -573,7 +573,7 @@
         <v>87.919921875</v>
       </c>
       <c r="G2">
-        <v>63.21</v>
+        <v>63.2099609375</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -596,7 +596,7 @@
         <v>78.47021484375</v>
       </c>
       <c r="G3">
-        <v>63.71</v>
+        <v>63.7099609375</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -619,7 +619,7 @@
         <v>63.8701171875</v>
       </c>
       <c r="G4">
-        <v>64.81</v>
+        <v>64.81005859375</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -642,7 +642,7 @@
         <v>82.31982421875</v>
       </c>
       <c r="G5">
-        <v>70.59999999999999</v>
+        <v>70.60009765625</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -665,7 +665,7 @@
         <v>93.06982421875</v>
       </c>
       <c r="G6">
-        <v>75.36</v>
+        <v>75.35986328125</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -688,7 +688,7 @@
         <v>86.419921875</v>
       </c>
       <c r="G7">
-        <v>47.39</v>
+        <v>47.389892578125</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -711,7 +711,7 @@
         <v>52.5400390625</v>
       </c>
       <c r="G8">
-        <v>34.55</v>
+        <v>34.550048828125</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -734,7 +734,7 @@
         <v>88.240234375</v>
       </c>
       <c r="G9">
-        <v>61.99</v>
+        <v>61.989990234375</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -757,7 +757,7 @@
         <v>41.169921875</v>
       </c>
       <c r="G10">
-        <v>71.01000000000001</v>
+        <v>71.009765625</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -780,7 +780,7 @@
         <v>87.72021484375</v>
       </c>
       <c r="G11">
-        <v>77.8</v>
+        <v>77.7998046875</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -803,7 +803,7 @@
         <v>84.81982421875</v>
       </c>
       <c r="G12">
-        <v>62.01</v>
+        <v>62.010009765625</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -826,7 +826,7 @@
         <v>77.22021484375</v>
       </c>
       <c r="G13">
-        <v>88.20999999999999</v>
+        <v>88.2099609375</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -849,7 +849,7 @@
         <v>85.669921875</v>
       </c>
       <c r="G14">
-        <v>58.61</v>
+        <v>58.610107421875</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -872,7 +872,7 @@
         <v>84.6201171875</v>
       </c>
       <c r="G15">
-        <v>75.81</v>
+        <v>75.81005859375</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -892,7 +892,7 @@
         <v>69.77001953125</v>
       </c>
       <c r="G16">
-        <v>47.99</v>
+        <v>47.989990234375</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -915,7 +915,7 @@
         <v>49.77001953125</v>
       </c>
       <c r="G17">
-        <v>55.38</v>
+        <v>55.3798828125</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -938,7 +938,7 @@
         <v>70.85986328125</v>
       </c>
       <c r="G18">
-        <v>67.59</v>
+        <v>67.58984375</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -961,7 +961,7 @@
         <v>72.759765625</v>
       </c>
       <c r="G19">
-        <v>61.2</v>
+        <v>61.199951171875</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -984,7 +984,7 @@
         <v>77.6201171875</v>
       </c>
       <c r="G20">
-        <v>79.01000000000001</v>
+        <v>79.009765625</v>
       </c>
     </row>
     <row r="21" spans="1:7">

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -575,6 +575,9 @@
       <c r="G2">
         <v>63.2099609375</v>
       </c>
+      <c r="H2">
+        <v>49.97</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -598,6 +601,9 @@
       <c r="G3">
         <v>63.7099609375</v>
       </c>
+      <c r="H3">
+        <v>35.7</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -621,6 +627,9 @@
       <c r="G4">
         <v>64.81005859375</v>
       </c>
+      <c r="H4">
+        <v>29.27</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -644,6 +653,9 @@
       <c r="G5">
         <v>70.60009765625</v>
       </c>
+      <c r="H5">
+        <v>31.8</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -667,6 +679,9 @@
       <c r="G6">
         <v>75.35986328125</v>
       </c>
+      <c r="H6">
+        <v>30.25</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -690,6 +705,9 @@
       <c r="G7">
         <v>47.389892578125</v>
       </c>
+      <c r="H7">
+        <v>38.87</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -713,6 +731,9 @@
       <c r="G8">
         <v>34.550048828125</v>
       </c>
+      <c r="H8">
+        <v>49.5</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -736,6 +757,9 @@
       <c r="G9">
         <v>61.989990234375</v>
       </c>
+      <c r="H9">
+        <v>28.9</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -759,6 +783,9 @@
       <c r="G10">
         <v>71.009765625</v>
       </c>
+      <c r="H10">
+        <v>40.27</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -782,6 +809,9 @@
       <c r="G11">
         <v>77.7998046875</v>
       </c>
+      <c r="H11">
+        <v>35.34</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -805,6 +835,9 @@
       <c r="G12">
         <v>62.010009765625</v>
       </c>
+      <c r="H12">
+        <v>30.77</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -828,6 +861,9 @@
       <c r="G13">
         <v>88.2099609375</v>
       </c>
+      <c r="H13">
+        <v>28.2</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -851,6 +887,9 @@
       <c r="G14">
         <v>58.610107421875</v>
       </c>
+      <c r="H14">
+        <v>45.37</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -874,6 +913,9 @@
       <c r="G15">
         <v>75.81005859375</v>
       </c>
+      <c r="H15">
+        <v>48.67</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -894,8 +936,11 @@
       <c r="G16">
         <v>47.989990234375</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16">
+        <v>24.05</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -917,8 +962,11 @@
       <c r="G17">
         <v>55.3798828125</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -940,8 +988,11 @@
       <c r="G18">
         <v>67.58984375</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18">
+        <v>32.97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -963,8 +1014,11 @@
       <c r="G19">
         <v>61.199951171875</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="H19">
+        <v>44.15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -986,8 +1040,11 @@
       <c r="G20">
         <v>79.009765625</v>
       </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="H20">
+        <v>41.27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1009,8 +1066,11 @@
       <c r="G21">
         <v>83</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21">
+        <v>43.17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1031,6 +1091,9 @@
       </c>
       <c r="G22" t="s">
         <v>30</v>
+      </c>
+      <c r="H22" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -576,7 +576,7 @@
         <v>63.2099609375</v>
       </c>
       <c r="H2">
-        <v>49.97</v>
+        <v>70.81982421875</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -602,7 +602,7 @@
         <v>63.7099609375</v>
       </c>
       <c r="H3">
-        <v>35.7</v>
+        <v>99.85986328125</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -628,7 +628,7 @@
         <v>64.81005859375</v>
       </c>
       <c r="H4">
-        <v>29.27</v>
+        <v>55.52001953125</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -654,7 +654,7 @@
         <v>70.60009765625</v>
       </c>
       <c r="H5">
-        <v>31.8</v>
+        <v>64.2099609375</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -680,7 +680,7 @@
         <v>75.35986328125</v>
       </c>
       <c r="H6">
-        <v>30.25</v>
+        <v>100.25</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -706,7 +706,7 @@
         <v>47.389892578125</v>
       </c>
       <c r="H7">
-        <v>38.87</v>
+        <v>67.27001953125</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -732,7 +732,7 @@
         <v>34.550048828125</v>
       </c>
       <c r="H8">
-        <v>49.5</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -758,7 +758,7 @@
         <v>61.989990234375</v>
       </c>
       <c r="H9">
-        <v>28.9</v>
+        <v>48.469970703125</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -784,7 +784,7 @@
         <v>71.009765625</v>
       </c>
       <c r="H10">
-        <v>40.27</v>
+        <v>65.47021484375</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -810,7 +810,7 @@
         <v>77.7998046875</v>
       </c>
       <c r="H11">
-        <v>35.34</v>
+        <v>57.93994140625</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -836,7 +836,7 @@
         <v>62.010009765625</v>
       </c>
       <c r="H12">
-        <v>30.77</v>
+        <v>77.06982421875</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -862,7 +862,7 @@
         <v>88.2099609375</v>
       </c>
       <c r="H13">
-        <v>28.2</v>
+        <v>61.110107421875</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -888,7 +888,7 @@
         <v>58.610107421875</v>
       </c>
       <c r="H14">
-        <v>45.37</v>
+        <v>81.56982421875</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -914,7 +914,7 @@
         <v>75.81005859375</v>
       </c>
       <c r="H15">
-        <v>48.67</v>
+        <v>83.22021484375</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -937,7 +937,7 @@
         <v>47.989990234375</v>
       </c>
       <c r="H16">
-        <v>24.05</v>
+        <v>46.550048828125</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -963,7 +963,7 @@
         <v>55.3798828125</v>
       </c>
       <c r="H17">
-        <v>12</v>
+        <v>61.8701171875</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -989,7 +989,7 @@
         <v>67.58984375</v>
       </c>
       <c r="H18">
-        <v>32.97</v>
+        <v>71.77001953125</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1015,7 +1015,7 @@
         <v>61.199951171875</v>
       </c>
       <c r="H19">
-        <v>44.15</v>
+        <v>69.60009765625</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1041,7 +1041,7 @@
         <v>79.009765625</v>
       </c>
       <c r="H20">
-        <v>41.27</v>
+        <v>65.47021484375</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1067,7 +1067,7 @@
         <v>83</v>
       </c>
       <c r="H21">
-        <v>43.17</v>
+        <v>76.97021484375</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1093,7 +1093,7 @@
         <v>30</v>
       </c>
       <c r="H22" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -578,6 +578,9 @@
       <c r="H2">
         <v>70.81982421875</v>
       </c>
+      <c r="I2">
+        <v>77.5498046875</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -604,6 +607,9 @@
       <c r="H3">
         <v>99.85986328125</v>
       </c>
+      <c r="I3">
+        <v>58.679931640625</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -630,6 +636,9 @@
       <c r="H4">
         <v>55.52001953125</v>
       </c>
+      <c r="I4">
+        <v>71.75</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -656,6 +665,9 @@
       <c r="H5">
         <v>64.2099609375</v>
       </c>
+      <c r="I5">
+        <v>83.0498046875</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -682,6 +694,9 @@
       <c r="H6">
         <v>100.25</v>
       </c>
+      <c r="I6">
+        <v>75.52001953125</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -708,6 +723,9 @@
       <c r="H7">
         <v>67.27001953125</v>
       </c>
+      <c r="I7">
+        <v>75.75</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -734,6 +752,9 @@
       <c r="H8">
         <v>61.5</v>
       </c>
+      <c r="I8">
+        <v>77</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -760,6 +781,9 @@
       <c r="H9">
         <v>48.469970703125</v>
       </c>
+      <c r="I9">
+        <v>82.85009765625</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -786,6 +810,9 @@
       <c r="H10">
         <v>65.47021484375</v>
       </c>
+      <c r="I10">
+        <v>34.110107421875</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -812,6 +839,9 @@
       <c r="H11">
         <v>57.93994140625</v>
       </c>
+      <c r="I11">
+        <v>42.89990234375</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -838,6 +868,9 @@
       <c r="H12">
         <v>77.06982421875</v>
       </c>
+      <c r="I12">
+        <v>80.0498046875</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -864,6 +897,9 @@
       <c r="H13">
         <v>61.110107421875</v>
       </c>
+      <c r="I13">
+        <v>82.81982421875</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -890,6 +926,9 @@
       <c r="H14">
         <v>81.56982421875</v>
       </c>
+      <c r="I14">
+        <v>73.35009765625</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -916,6 +955,9 @@
       <c r="H15">
         <v>83.22021484375</v>
       </c>
+      <c r="I15">
+        <v>85.64990234375</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -939,8 +981,11 @@
       <c r="H16">
         <v>46.550048828125</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16">
+        <v>59.909912109375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -965,8 +1010,11 @@
       <c r="H17">
         <v>61.8701171875</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17">
+        <v>70.5400390625</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -991,8 +1039,11 @@
       <c r="H18">
         <v>71.77001953125</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18">
+        <v>68.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1017,8 +1068,11 @@
       <c r="H19">
         <v>69.60009765625</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19">
+        <v>67.14990234375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1043,8 +1097,11 @@
       <c r="H20">
         <v>65.47021484375</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20">
+        <v>80.85009765625</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1069,8 +1126,11 @@
       <c r="H21">
         <v>76.97021484375</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="I21">
+        <v>76.4501953125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1094,6 +1154,9 @@
       </c>
       <c r="H22" t="s">
         <v>23</v>
+      </c>
+      <c r="I22" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -581,6 +581,9 @@
       <c r="I2">
         <v>77.5498046875</v>
       </c>
+      <c r="J2">
+        <v>73.68000000000001</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -610,6 +613,9 @@
       <c r="I3">
         <v>58.679931640625</v>
       </c>
+      <c r="J3">
+        <v>88.64</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -639,6 +645,9 @@
       <c r="I4">
         <v>71.75</v>
       </c>
+      <c r="J4">
+        <v>49.76</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -668,6 +677,9 @@
       <c r="I5">
         <v>83.0498046875</v>
       </c>
+      <c r="J5">
+        <v>97.95999999999999</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -697,6 +709,9 @@
       <c r="I6">
         <v>75.52001953125</v>
       </c>
+      <c r="J6">
+        <v>71.98</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -726,6 +741,9 @@
       <c r="I7">
         <v>75.75</v>
       </c>
+      <c r="J7">
+        <v>85.95999999999999</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -755,6 +773,9 @@
       <c r="I8">
         <v>77</v>
       </c>
+      <c r="J8">
+        <v>68.68000000000001</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -784,6 +805,9 @@
       <c r="I9">
         <v>82.85009765625</v>
       </c>
+      <c r="J9">
+        <v>85.53</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -813,6 +837,9 @@
       <c r="I10">
         <v>34.110107421875</v>
       </c>
+      <c r="J10">
+        <v>70.73999999999999</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -842,6 +869,9 @@
       <c r="I11">
         <v>42.89990234375</v>
       </c>
+      <c r="J11">
+        <v>97.68000000000001</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -871,6 +901,9 @@
       <c r="I12">
         <v>80.0498046875</v>
       </c>
+      <c r="J12">
+        <v>61.01</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -900,6 +933,9 @@
       <c r="I13">
         <v>82.81982421875</v>
       </c>
+      <c r="J13">
+        <v>87.44</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -929,6 +965,9 @@
       <c r="I14">
         <v>73.35009765625</v>
       </c>
+      <c r="J14">
+        <v>104.68</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -958,6 +997,9 @@
       <c r="I15">
         <v>85.64990234375</v>
       </c>
+      <c r="J15">
+        <v>68.44</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -984,8 +1026,11 @@
       <c r="I16">
         <v>59.909912109375</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="J16">
+        <v>70.48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1013,8 +1058,11 @@
       <c r="I17">
         <v>70.5400390625</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="J17">
+        <v>39.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1042,8 +1090,11 @@
       <c r="I18">
         <v>68.25</v>
       </c>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="J18">
+        <v>80.34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1071,8 +1122,11 @@
       <c r="I19">
         <v>67.14990234375</v>
       </c>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="J19">
+        <v>61.98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1100,8 +1154,11 @@
       <c r="I20">
         <v>80.85009765625</v>
       </c>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="J20">
+        <v>94.28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1129,8 +1186,11 @@
       <c r="I21">
         <v>76.4501953125</v>
       </c>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="J21">
+        <v>86.43000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1157,6 +1217,9 @@
       </c>
       <c r="I22" t="s">
         <v>32</v>
+      </c>
+      <c r="J22" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -582,7 +582,7 @@
         <v>77.5498046875</v>
       </c>
       <c r="J2">
-        <v>73.68000000000001</v>
+        <v>73.68017578125</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -614,7 +614,7 @@
         <v>58.679931640625</v>
       </c>
       <c r="J3">
-        <v>88.64</v>
+        <v>87.14013671875</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -646,7 +646,7 @@
         <v>71.75</v>
       </c>
       <c r="J4">
-        <v>49.76</v>
+        <v>49.760009765625</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -678,7 +678,7 @@
         <v>83.0498046875</v>
       </c>
       <c r="J5">
-        <v>97.95999999999999</v>
+        <v>97.9599609375</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -710,7 +710,7 @@
         <v>75.52001953125</v>
       </c>
       <c r="J6">
-        <v>71.98</v>
+        <v>70.10009765625</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -742,7 +742,7 @@
         <v>75.75</v>
       </c>
       <c r="J7">
-        <v>85.95999999999999</v>
+        <v>85.9599609375</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -774,7 +774,7 @@
         <v>77</v>
       </c>
       <c r="J8">
-        <v>68.68000000000001</v>
+        <v>68.68017578125</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -806,7 +806,7 @@
         <v>82.85009765625</v>
       </c>
       <c r="J9">
-        <v>85.53</v>
+        <v>85.52978515625</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -838,7 +838,7 @@
         <v>34.110107421875</v>
       </c>
       <c r="J10">
-        <v>70.73999999999999</v>
+        <v>70.740234375</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -870,7 +870,7 @@
         <v>42.89990234375</v>
       </c>
       <c r="J11">
-        <v>97.68000000000001</v>
+        <v>97.68017578125</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -902,7 +902,7 @@
         <v>80.0498046875</v>
       </c>
       <c r="J12">
-        <v>61.01</v>
+        <v>59.010009765625</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -934,7 +934,7 @@
         <v>82.81982421875</v>
       </c>
       <c r="J13">
-        <v>87.44</v>
+        <v>85.93994140625</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -966,7 +966,7 @@
         <v>73.35009765625</v>
       </c>
       <c r="J14">
-        <v>104.68</v>
+        <v>104.68017578125</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -998,7 +998,7 @@
         <v>85.64990234375</v>
       </c>
       <c r="J15">
-        <v>68.44</v>
+        <v>66.93994140625</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1027,7 +1027,7 @@
         <v>59.909912109375</v>
       </c>
       <c r="J16">
-        <v>70.48</v>
+        <v>70.47998046875</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1059,7 +1059,7 @@
         <v>70.5400390625</v>
       </c>
       <c r="J17">
-        <v>39.7</v>
+        <v>39.699951171875</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1091,7 +1091,7 @@
         <v>68.25</v>
       </c>
       <c r="J18">
-        <v>80.34</v>
+        <v>80.33984375</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1123,7 +1123,7 @@
         <v>67.14990234375</v>
       </c>
       <c r="J19">
-        <v>61.98</v>
+        <v>62.89990234375</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1155,7 +1155,7 @@
         <v>80.85009765625</v>
       </c>
       <c r="J20">
-        <v>94.28</v>
+        <v>94.27978515625</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1187,7 +1187,7 @@
         <v>76.4501953125</v>
       </c>
       <c r="J21">
-        <v>86.43000000000001</v>
+        <v>85.85009765625</v>
       </c>
     </row>
     <row r="22" spans="1:10">

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -584,6 +584,9 @@
       <c r="J2">
         <v>73.68017578125</v>
       </c>
+      <c r="K2">
+        <v>31.57</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -616,6 +619,9 @@
       <c r="J3">
         <v>87.14013671875</v>
       </c>
+      <c r="K3">
+        <v>56.47</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -648,6 +654,9 @@
       <c r="J4">
         <v>49.760009765625</v>
       </c>
+      <c r="K4">
+        <v>39.58</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -680,6 +689,9 @@
       <c r="J5">
         <v>97.9599609375</v>
       </c>
+      <c r="K5">
+        <v>69.06999999999999</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -712,6 +724,9 @@
       <c r="J6">
         <v>70.10009765625</v>
       </c>
+      <c r="K6">
+        <v>42.89</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -744,6 +759,9 @@
       <c r="J7">
         <v>85.9599609375</v>
       </c>
+      <c r="K7">
+        <v>39.87</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -776,6 +794,9 @@
       <c r="J8">
         <v>68.68017578125</v>
       </c>
+      <c r="K8">
+        <v>19.4</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -808,6 +829,9 @@
       <c r="J9">
         <v>85.52978515625</v>
       </c>
+      <c r="K9">
+        <v>55.58</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -840,6 +864,9 @@
       <c r="J10">
         <v>70.740234375</v>
       </c>
+      <c r="K10">
+        <v>54.48</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -872,6 +899,9 @@
       <c r="J11">
         <v>97.68017578125</v>
       </c>
+      <c r="K11">
+        <v>66.56999999999999</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -904,6 +934,9 @@
       <c r="J12">
         <v>59.010009765625</v>
       </c>
+      <c r="K12">
+        <v>60.57</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -936,6 +969,9 @@
       <c r="J13">
         <v>85.93994140625</v>
       </c>
+      <c r="K13">
+        <v>43.59</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -968,6 +1004,9 @@
       <c r="J14">
         <v>104.68017578125</v>
       </c>
+      <c r="K14">
+        <v>67.29000000000001</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -1000,6 +1039,9 @@
       <c r="J15">
         <v>66.93994140625</v>
       </c>
+      <c r="K15">
+        <v>59.75</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -1029,8 +1071,11 @@
       <c r="J16">
         <v>70.47998046875</v>
       </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="K16">
+        <v>67.78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1061,8 +1106,11 @@
       <c r="J17">
         <v>39.699951171875</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="K17">
+        <v>32.15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1093,8 +1141,11 @@
       <c r="J18">
         <v>80.33984375</v>
       </c>
-    </row>
-    <row r="19" spans="1:10">
+      <c r="K18">
+        <v>60.45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1125,8 +1176,11 @@
       <c r="J19">
         <v>62.89990234375</v>
       </c>
-    </row>
-    <row r="20" spans="1:10">
+      <c r="K19">
+        <v>44.05</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1157,8 +1211,11 @@
       <c r="J20">
         <v>94.27978515625</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20">
+        <v>71.17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1189,8 +1246,11 @@
       <c r="J21">
         <v>85.85009765625</v>
       </c>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="K21">
+        <v>59.29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1220,6 +1280,9 @@
       </c>
       <c r="J22" t="s">
         <v>31</v>
+      </c>
+      <c r="K22" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -585,7 +585,7 @@
         <v>73.68017578125</v>
       </c>
       <c r="K2">
-        <v>31.57</v>
+        <v>30.3699951171875</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -620,7 +620,7 @@
         <v>87.14013671875</v>
       </c>
       <c r="K3">
-        <v>56.47</v>
+        <v>55.27001953125</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -655,7 +655,7 @@
         <v>49.760009765625</v>
       </c>
       <c r="K4">
-        <v>39.58</v>
+        <v>38.780029296875</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -690,7 +690,7 @@
         <v>97.9599609375</v>
       </c>
       <c r="K5">
-        <v>69.06999999999999</v>
+        <v>68.669921875</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -725,7 +725,7 @@
         <v>70.10009765625</v>
       </c>
       <c r="K6">
-        <v>42.89</v>
+        <v>42.090087890625</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -760,7 +760,7 @@
         <v>85.9599609375</v>
       </c>
       <c r="K7">
-        <v>39.87</v>
+        <v>39.469970703125</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -795,7 +795,7 @@
         <v>68.68017578125</v>
       </c>
       <c r="K8">
-        <v>19.4</v>
+        <v>19.4000244140625</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -830,7 +830,7 @@
         <v>85.52978515625</v>
       </c>
       <c r="K9">
-        <v>55.58</v>
+        <v>55.179931640625</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -865,7 +865,7 @@
         <v>70.740234375</v>
       </c>
       <c r="K10">
-        <v>54.48</v>
+        <v>53.280029296875</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -900,7 +900,7 @@
         <v>97.68017578125</v>
       </c>
       <c r="K11">
-        <v>66.56999999999999</v>
+        <v>65.3701171875</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -935,7 +935,7 @@
         <v>59.010009765625</v>
       </c>
       <c r="K12">
-        <v>60.57</v>
+        <v>60.169921875</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -970,7 +970,7 @@
         <v>85.93994140625</v>
       </c>
       <c r="K13">
-        <v>43.59</v>
+        <v>43.590087890625</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1005,7 +1005,7 @@
         <v>104.68017578125</v>
       </c>
       <c r="K14">
-        <v>67.29000000000001</v>
+        <v>66.89013671875</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1040,7 +1040,7 @@
         <v>66.93994140625</v>
       </c>
       <c r="K15">
-        <v>59.75</v>
+        <v>58.949951171875</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1072,7 +1072,7 @@
         <v>70.47998046875</v>
       </c>
       <c r="K16">
-        <v>67.78</v>
+        <v>66.580078125</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1107,7 +1107,7 @@
         <v>39.699951171875</v>
       </c>
       <c r="K17">
-        <v>32.15</v>
+        <v>31.75</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1142,7 +1142,7 @@
         <v>80.33984375</v>
       </c>
       <c r="K18">
-        <v>60.45</v>
+        <v>60.050048828125</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1177,7 +1177,7 @@
         <v>62.89990234375</v>
       </c>
       <c r="K19">
-        <v>44.05</v>
+        <v>43.25</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1212,7 +1212,7 @@
         <v>94.27978515625</v>
       </c>
       <c r="K20">
-        <v>71.17</v>
+        <v>70.77001953125</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1247,7 +1247,7 @@
         <v>85.85009765625</v>
       </c>
       <c r="K21">
-        <v>59.29</v>
+        <v>58.090087890625</v>
       </c>
     </row>
     <row r="22" spans="1:11">

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -587,6 +587,9 @@
       <c r="K2">
         <v>30.3699951171875</v>
       </c>
+      <c r="L2">
+        <v>107.56005859375</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -622,6 +625,9 @@
       <c r="K3">
         <v>55.27001953125</v>
       </c>
+      <c r="L3">
+        <v>81.35986328125</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -657,6 +663,9 @@
       <c r="K4">
         <v>38.780029296875</v>
       </c>
+      <c r="L4">
+        <v>88.06005859375</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -692,6 +701,9 @@
       <c r="K5">
         <v>68.669921875</v>
       </c>
+      <c r="L5">
+        <v>92.16015625</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -727,6 +739,9 @@
       <c r="K6">
         <v>42.090087890625</v>
       </c>
+      <c r="L6">
+        <v>70.9599609375</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -762,6 +777,9 @@
       <c r="K7">
         <v>39.469970703125</v>
       </c>
+      <c r="L7">
+        <v>85.16015625</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -797,6 +815,9 @@
       <c r="K8">
         <v>19.4000244140625</v>
       </c>
+      <c r="L8">
+        <v>95.259765625</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -832,6 +853,9 @@
       <c r="K9">
         <v>55.179931640625</v>
       </c>
+      <c r="L9">
+        <v>93.68017578125</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -867,6 +891,9 @@
       <c r="K10">
         <v>53.280029296875</v>
       </c>
+      <c r="L10">
+        <v>96.4599609375</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -902,6 +929,9 @@
       <c r="K11">
         <v>65.3701171875</v>
       </c>
+      <c r="L11">
+        <v>82.4599609375</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -937,6 +967,9 @@
       <c r="K12">
         <v>60.169921875</v>
       </c>
+      <c r="L12">
+        <v>82.81005859375</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -972,6 +1005,9 @@
       <c r="K13">
         <v>43.590087890625</v>
       </c>
+      <c r="L13">
+        <v>86.9599609375</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -1007,6 +1043,9 @@
       <c r="K14">
         <v>66.89013671875</v>
       </c>
+      <c r="L14">
+        <v>90.4599609375</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -1042,6 +1081,9 @@
       <c r="K15">
         <v>58.949951171875</v>
       </c>
+      <c r="L15">
+        <v>92.66015625</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -1074,8 +1116,11 @@
       <c r="K16">
         <v>66.580078125</v>
       </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16">
+        <v>29.8499755859375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1109,8 +1154,11 @@
       <c r="K17">
         <v>31.75</v>
       </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17">
+        <v>51.530029296875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1144,8 +1192,11 @@
       <c r="K18">
         <v>60.050048828125</v>
       </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18">
+        <v>89.66015625</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1179,8 +1230,11 @@
       <c r="K19">
         <v>43.25</v>
       </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19">
+        <v>81.8798828125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1214,8 +1268,11 @@
       <c r="K20">
         <v>70.77001953125</v>
       </c>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="L20">
+        <v>98.56005859375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1249,8 +1306,11 @@
       <c r="K21">
         <v>58.090087890625</v>
       </c>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="L21">
+        <v>88.759765625</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1283,6 +1343,9 @@
       </c>
       <c r="K22" t="s">
         <v>37</v>
+      </c>
+      <c r="L22" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -590,6 +590,9 @@
       <c r="L2">
         <v>107.56005859375</v>
       </c>
+      <c r="M2">
+        <v>66.11</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -628,6 +631,9 @@
       <c r="L3">
         <v>81.35986328125</v>
       </c>
+      <c r="M3">
+        <v>68.5</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -666,6 +672,9 @@
       <c r="L4">
         <v>88.06005859375</v>
       </c>
+      <c r="M4">
+        <v>65.84999999999999</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -704,6 +713,9 @@
       <c r="L5">
         <v>92.16015625</v>
       </c>
+      <c r="M5">
+        <v>66.40000000000001</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -742,6 +754,9 @@
       <c r="L6">
         <v>70.9599609375</v>
       </c>
+      <c r="M6">
+        <v>100</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -780,6 +795,9 @@
       <c r="L7">
         <v>85.16015625</v>
       </c>
+      <c r="M7">
+        <v>81.45</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -818,6 +836,9 @@
       <c r="L8">
         <v>95.259765625</v>
       </c>
+      <c r="M8">
+        <v>72.09999999999999</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -856,6 +877,9 @@
       <c r="L9">
         <v>93.68017578125</v>
       </c>
+      <c r="M9">
+        <v>75</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -894,6 +918,9 @@
       <c r="L10">
         <v>96.4599609375</v>
       </c>
+      <c r="M10">
+        <v>64.92</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -932,6 +959,9 @@
       <c r="L11">
         <v>82.4599609375</v>
       </c>
+      <c r="M11">
+        <v>69.90000000000001</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -970,6 +1000,9 @@
       <c r="L12">
         <v>82.81005859375</v>
       </c>
+      <c r="M12">
+        <v>77.34999999999999</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -1008,6 +1041,9 @@
       <c r="L13">
         <v>86.9599609375</v>
       </c>
+      <c r="M13">
+        <v>101.25</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -1046,6 +1082,9 @@
       <c r="L14">
         <v>90.4599609375</v>
       </c>
+      <c r="M14">
+        <v>84.40000000000001</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -1084,6 +1123,9 @@
       <c r="L15">
         <v>92.66015625</v>
       </c>
+      <c r="M15">
+        <v>76.8</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -1119,8 +1161,11 @@
       <c r="L16">
         <v>29.8499755859375</v>
       </c>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="M16">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1157,8 +1202,11 @@
       <c r="L17">
         <v>51.530029296875</v>
       </c>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="M17">
+        <v>35.29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1195,8 +1243,11 @@
       <c r="L18">
         <v>89.66015625</v>
       </c>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="M18">
+        <v>81.95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1233,8 +1284,11 @@
       <c r="L19">
         <v>81.8798828125</v>
       </c>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="M19">
+        <v>41.57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1271,8 +1325,11 @@
       <c r="L20">
         <v>98.56005859375</v>
       </c>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="M20">
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1309,8 +1366,11 @@
       <c r="L21">
         <v>88.759765625</v>
       </c>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="M21">
+        <v>86.66</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1346,6 +1406,9 @@
       </c>
       <c r="L22" t="s">
         <v>19</v>
+      </c>
+      <c r="M22" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -591,7 +591,7 @@
         <v>107.56005859375</v>
       </c>
       <c r="M2">
-        <v>66.11</v>
+        <v>66.10986328125</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -673,7 +673,7 @@
         <v>88.06005859375</v>
       </c>
       <c r="M4">
-        <v>65.84999999999999</v>
+        <v>65.85009765625</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -714,7 +714,7 @@
         <v>92.16015625</v>
       </c>
       <c r="M5">
-        <v>66.40000000000001</v>
+        <v>66.39990234375</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -796,7 +796,7 @@
         <v>85.16015625</v>
       </c>
       <c r="M7">
-        <v>81.45</v>
+        <v>81.4501953125</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -837,7 +837,7 @@
         <v>95.259765625</v>
       </c>
       <c r="M8">
-        <v>72.09999999999999</v>
+        <v>72.10009765625</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -919,7 +919,7 @@
         <v>96.4599609375</v>
       </c>
       <c r="M10">
-        <v>64.92</v>
+        <v>64.919921875</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -960,7 +960,7 @@
         <v>82.4599609375</v>
       </c>
       <c r="M11">
-        <v>69.90000000000001</v>
+        <v>69.89990234375</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1001,7 +1001,7 @@
         <v>82.81005859375</v>
       </c>
       <c r="M12">
-        <v>77.34999999999999</v>
+        <v>77.35009765625</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1083,7 +1083,7 @@
         <v>90.4599609375</v>
       </c>
       <c r="M14">
-        <v>84.40000000000001</v>
+        <v>84.39990234375</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1124,7 +1124,7 @@
         <v>92.66015625</v>
       </c>
       <c r="M15">
-        <v>76.8</v>
+        <v>76.7998046875</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1162,7 +1162,7 @@
         <v>29.8499755859375</v>
       </c>
       <c r="M16">
-        <v>57.1</v>
+        <v>57.10009765625</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1203,7 +1203,7 @@
         <v>51.530029296875</v>
       </c>
       <c r="M17">
-        <v>35.29</v>
+        <v>35.2900390625</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -1244,7 +1244,7 @@
         <v>89.66015625</v>
       </c>
       <c r="M18">
-        <v>81.95</v>
+        <v>81.9501953125</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -1285,7 +1285,7 @@
         <v>81.8798828125</v>
       </c>
       <c r="M19">
-        <v>41.57</v>
+        <v>41.570068359375</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -1367,7 +1367,7 @@
         <v>88.759765625</v>
       </c>
       <c r="M21">
-        <v>86.66</v>
+        <v>86.66015625</v>
       </c>
     </row>
     <row r="22" spans="1:13">

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -593,6 +593,9 @@
       <c r="M2">
         <v>66.10986328125</v>
       </c>
+      <c r="N2">
+        <v>99.31999999999999</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -634,6 +637,9 @@
       <c r="M3">
         <v>68.5</v>
       </c>
+      <c r="N3">
+        <v>88.47</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -675,6 +681,9 @@
       <c r="M4">
         <v>65.85009765625</v>
       </c>
+      <c r="N4">
+        <v>90.37</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -716,6 +725,9 @@
       <c r="M5">
         <v>66.39990234375</v>
       </c>
+      <c r="N5">
+        <v>102.42</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -757,6 +769,9 @@
       <c r="M6">
         <v>100</v>
       </c>
+      <c r="N6">
+        <v>92.52</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -798,6 +813,9 @@
       <c r="M7">
         <v>81.4501953125</v>
       </c>
+      <c r="N7">
+        <v>113.22</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -839,6 +857,9 @@
       <c r="M8">
         <v>72.10009765625</v>
       </c>
+      <c r="N8">
+        <v>119.03</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -880,6 +901,9 @@
       <c r="M9">
         <v>75</v>
       </c>
+      <c r="N9">
+        <v>108.98</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -921,6 +945,9 @@
       <c r="M10">
         <v>64.919921875</v>
       </c>
+      <c r="N10">
+        <v>99.97</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -962,6 +989,9 @@
       <c r="M11">
         <v>69.89990234375</v>
       </c>
+      <c r="N11">
+        <v>108.52</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -1003,6 +1033,9 @@
       <c r="M12">
         <v>77.35009765625</v>
       </c>
+      <c r="N12">
+        <v>91.87</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -1044,6 +1077,9 @@
       <c r="M13">
         <v>101.25</v>
       </c>
+      <c r="N13">
+        <v>90.02</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -1085,6 +1121,9 @@
       <c r="M14">
         <v>84.39990234375</v>
       </c>
+      <c r="N14">
+        <v>108.52</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -1126,6 +1165,9 @@
       <c r="M15">
         <v>76.7998046875</v>
       </c>
+      <c r="N15">
+        <v>85.94</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -1164,8 +1206,11 @@
       <c r="M16">
         <v>57.10009765625</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="N16">
+        <v>31.05</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1205,8 +1250,11 @@
       <c r="M17">
         <v>35.2900390625</v>
       </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="N17">
+        <v>54.83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1246,8 +1294,11 @@
       <c r="M18">
         <v>81.9501953125</v>
       </c>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="N18">
+        <v>92.22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1287,8 +1338,11 @@
       <c r="M19">
         <v>41.570068359375</v>
       </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19">
+        <v>96.77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1328,8 +1382,11 @@
       <c r="M20">
         <v>83.5</v>
       </c>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="N20">
+        <v>114.52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1369,8 +1426,11 @@
       <c r="M21">
         <v>86.66015625</v>
       </c>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="N21">
+        <v>97.62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1409,6 +1469,9 @@
       </c>
       <c r="M22" t="s">
         <v>30</v>
+      </c>
+      <c r="N22" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -594,7 +594,7 @@
         <v>66.10986328125</v>
       </c>
       <c r="N2">
-        <v>99.31999999999999</v>
+        <v>99.39</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -638,7 +638,7 @@
         <v>68.5</v>
       </c>
       <c r="N3">
-        <v>88.47</v>
+        <v>88.04000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -682,7 +682,7 @@
         <v>65.85009765625</v>
       </c>
       <c r="N4">
-        <v>90.37</v>
+        <v>98.44</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -726,7 +726,7 @@
         <v>66.39990234375</v>
       </c>
       <c r="N5">
-        <v>102.42</v>
+        <v>112.29</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -770,7 +770,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>92.52</v>
+        <v>100.59</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -814,7 +814,7 @@
         <v>81.4501953125</v>
       </c>
       <c r="N7">
-        <v>113.22</v>
+        <v>113.29</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -858,7 +858,7 @@
         <v>72.10009765625</v>
       </c>
       <c r="N8">
-        <v>119.03</v>
+        <v>118.53</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -902,7 +902,7 @@
         <v>75</v>
       </c>
       <c r="N9">
-        <v>108.98</v>
+        <v>108.48</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -946,7 +946,7 @@
         <v>64.919921875</v>
       </c>
       <c r="N10">
-        <v>99.97</v>
+        <v>118.24</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -990,7 +990,7 @@
         <v>69.89990234375</v>
       </c>
       <c r="N11">
-        <v>108.52</v>
+        <v>108.59</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1034,7 +1034,7 @@
         <v>77.35009765625</v>
       </c>
       <c r="N12">
-        <v>91.87</v>
+        <v>115.44</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1078,7 +1078,7 @@
         <v>101.25</v>
       </c>
       <c r="N13">
-        <v>90.02</v>
+        <v>102.99</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1122,7 +1122,7 @@
         <v>84.39990234375</v>
       </c>
       <c r="N14">
-        <v>108.52</v>
+        <v>108.59</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1295,7 +1295,7 @@
         <v>81.9501953125</v>
       </c>
       <c r="N18">
-        <v>92.22</v>
+        <v>113.19</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1339,7 +1339,7 @@
         <v>41.570068359375</v>
       </c>
       <c r="N19">
-        <v>96.77</v>
+        <v>96.84</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1383,7 +1383,7 @@
         <v>83.5</v>
       </c>
       <c r="N20">
-        <v>114.52</v>
+        <v>114.09</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1427,7 +1427,7 @@
         <v>86.66015625</v>
       </c>
       <c r="N21">
-        <v>97.62</v>
+        <v>106.39</v>
       </c>
     </row>
     <row r="22" spans="1:14">

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -594,7 +594,7 @@
         <v>66.10986328125</v>
       </c>
       <c r="N2">
-        <v>99.39</v>
+        <v>99.39013671875</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -638,7 +638,7 @@
         <v>68.5</v>
       </c>
       <c r="N3">
-        <v>88.04000000000001</v>
+        <v>88.0400390625</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -682,7 +682,7 @@
         <v>65.85009765625</v>
       </c>
       <c r="N4">
-        <v>98.44</v>
+        <v>98.43994140625</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -726,7 +726,7 @@
         <v>66.39990234375</v>
       </c>
       <c r="N5">
-        <v>112.29</v>
+        <v>112.2900390625</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -770,7 +770,7 @@
         <v>100</v>
       </c>
       <c r="N6">
-        <v>100.59</v>
+        <v>100.58984375</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -814,7 +814,7 @@
         <v>81.4501953125</v>
       </c>
       <c r="N7">
-        <v>113.29</v>
+        <v>113.2900390625</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -858,7 +858,7 @@
         <v>72.10009765625</v>
       </c>
       <c r="N8">
-        <v>118.53</v>
+        <v>118.43994140625</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -902,7 +902,7 @@
         <v>75</v>
       </c>
       <c r="N9">
-        <v>108.48</v>
+        <v>108.39013671875</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -946,7 +946,7 @@
         <v>64.919921875</v>
       </c>
       <c r="N10">
-        <v>118.24</v>
+        <v>118.240234375</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -990,7 +990,7 @@
         <v>69.89990234375</v>
       </c>
       <c r="N11">
-        <v>108.59</v>
+        <v>108.58984375</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1034,7 +1034,7 @@
         <v>77.35009765625</v>
       </c>
       <c r="N12">
-        <v>115.44</v>
+        <v>115.43994140625</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1078,7 +1078,7 @@
         <v>101.25</v>
       </c>
       <c r="N13">
-        <v>102.99</v>
+        <v>102.990234375</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1122,7 +1122,7 @@
         <v>84.39990234375</v>
       </c>
       <c r="N14">
-        <v>108.59</v>
+        <v>108.58984375</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1166,7 +1166,7 @@
         <v>76.7998046875</v>
       </c>
       <c r="N15">
-        <v>85.94</v>
+        <v>85.93994140625</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1207,7 +1207,7 @@
         <v>57.10009765625</v>
       </c>
       <c r="N16">
-        <v>31.05</v>
+        <v>31.050048828125</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1251,7 +1251,7 @@
         <v>35.2900390625</v>
       </c>
       <c r="N17">
-        <v>54.83</v>
+        <v>54.830078125</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1295,7 +1295,7 @@
         <v>81.9501953125</v>
       </c>
       <c r="N18">
-        <v>113.19</v>
+        <v>113.18994140625</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1339,7 +1339,7 @@
         <v>41.570068359375</v>
       </c>
       <c r="N19">
-        <v>96.84</v>
+        <v>96.83984375</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1383,7 +1383,7 @@
         <v>83.5</v>
       </c>
       <c r="N20">
-        <v>114.09</v>
+        <v>114.08984375</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1427,7 +1427,7 @@
         <v>86.66015625</v>
       </c>
       <c r="N21">
-        <v>106.39</v>
+        <v>106.39013671875</v>
       </c>
     </row>
     <row r="22" spans="1:14">

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -596,6 +596,9 @@
       <c r="N2">
         <v>99.39013671875</v>
       </c>
+      <c r="O2">
+        <v>57.8798828125</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -640,6 +643,9 @@
       <c r="N3">
         <v>88.0400390625</v>
       </c>
+      <c r="O3">
+        <v>69.4501953125</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -684,6 +690,9 @@
       <c r="N4">
         <v>98.43994140625</v>
       </c>
+      <c r="O4">
+        <v>78.4501953125</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -728,6 +737,9 @@
       <c r="N5">
         <v>112.2900390625</v>
       </c>
+      <c r="O5">
+        <v>55.139892578125</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -772,6 +784,9 @@
       <c r="N6">
         <v>100.58984375</v>
       </c>
+      <c r="O6">
+        <v>53.25</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -816,6 +831,9 @@
       <c r="N7">
         <v>113.2900390625</v>
       </c>
+      <c r="O7">
+        <v>61.949951171875</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -860,6 +878,9 @@
       <c r="N8">
         <v>118.43994140625</v>
       </c>
+      <c r="O8">
+        <v>70.14013671875</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -904,6 +925,9 @@
       <c r="N9">
         <v>108.39013671875</v>
       </c>
+      <c r="O9">
+        <v>67.83984375</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -948,6 +972,9 @@
       <c r="N10">
         <v>118.240234375</v>
       </c>
+      <c r="O10">
+        <v>58.43994140625</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -992,6 +1019,9 @@
       <c r="N11">
         <v>108.58984375</v>
       </c>
+      <c r="O11">
+        <v>71.25</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -1036,6 +1066,9 @@
       <c r="N12">
         <v>115.43994140625</v>
       </c>
+      <c r="O12">
+        <v>57.72998046875</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -1080,6 +1113,9 @@
       <c r="N13">
         <v>102.990234375</v>
       </c>
+      <c r="O13">
+        <v>66.080078125</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -1124,6 +1160,9 @@
       <c r="N14">
         <v>108.58984375</v>
       </c>
+      <c r="O14">
+        <v>49.280029296875</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -1168,6 +1207,9 @@
       <c r="N15">
         <v>85.93994140625</v>
       </c>
+      <c r="O15">
+        <v>66.0498046875</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -1209,8 +1251,11 @@
       <c r="N16">
         <v>31.050048828125</v>
       </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16">
+        <v>31.6500244140625</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1253,8 +1298,11 @@
       <c r="N17">
         <v>54.830078125</v>
       </c>
-    </row>
-    <row r="18" spans="1:14">
+      <c r="O17">
+        <v>30.030029296875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1297,8 +1345,11 @@
       <c r="N18">
         <v>113.18994140625</v>
       </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="O18">
+        <v>50.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1341,8 +1392,11 @@
       <c r="N19">
         <v>96.83984375</v>
       </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19">
+        <v>47.43994140625</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1385,8 +1439,11 @@
       <c r="N20">
         <v>114.08984375</v>
       </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="O20">
+        <v>57.14990234375</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1429,8 +1486,11 @@
       <c r="N21">
         <v>106.39013671875</v>
       </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="O21">
+        <v>53.780029296875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1472,6 +1532,9 @@
       </c>
       <c r="N22" t="s">
         <v>25</v>
+      </c>
+      <c r="O22" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -599,6 +599,9 @@
       <c r="O2">
         <v>57.8798828125</v>
       </c>
+      <c r="P2">
+        <v>45.78</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -646,6 +649,9 @@
       <c r="O3">
         <v>69.4501953125</v>
       </c>
+      <c r="P3">
+        <v>50.98</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -693,6 +699,9 @@
       <c r="O4">
         <v>78.4501953125</v>
       </c>
+      <c r="P4">
+        <v>45.15</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -740,6 +749,9 @@
       <c r="O5">
         <v>55.139892578125</v>
       </c>
+      <c r="P5">
+        <v>58.04</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -787,6 +799,9 @@
       <c r="O6">
         <v>53.25</v>
       </c>
+      <c r="P6">
+        <v>39.12</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -834,6 +849,9 @@
       <c r="O7">
         <v>61.949951171875</v>
       </c>
+      <c r="P7">
+        <v>60.17</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -881,6 +899,9 @@
       <c r="O8">
         <v>70.14013671875</v>
       </c>
+      <c r="P8">
+        <v>81.98</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -928,6 +949,9 @@
       <c r="O9">
         <v>67.83984375</v>
       </c>
+      <c r="P9">
+        <v>64.2</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -975,6 +999,9 @@
       <c r="O10">
         <v>58.43994140625</v>
       </c>
+      <c r="P10">
+        <v>50.2</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -1022,6 +1049,9 @@
       <c r="O11">
         <v>71.25</v>
       </c>
+      <c r="P11">
+        <v>55.52</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -1069,6 +1099,9 @@
       <c r="O12">
         <v>57.72998046875</v>
       </c>
+      <c r="P12">
+        <v>55.9</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -1116,6 +1149,9 @@
       <c r="O13">
         <v>66.080078125</v>
       </c>
+      <c r="P13">
+        <v>49.62</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -1163,6 +1199,9 @@
       <c r="O14">
         <v>49.280029296875</v>
       </c>
+      <c r="P14">
+        <v>54.58</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -1210,6 +1249,9 @@
       <c r="O15">
         <v>66.0498046875</v>
       </c>
+      <c r="P15">
+        <v>35.42</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -1254,8 +1296,11 @@
       <c r="O16">
         <v>31.6500244140625</v>
       </c>
-    </row>
-    <row r="17" spans="1:15">
+      <c r="P16">
+        <v>31.34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1301,8 +1346,11 @@
       <c r="O17">
         <v>30.030029296875</v>
       </c>
-    </row>
-    <row r="18" spans="1:15">
+      <c r="P17">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1348,8 +1396,11 @@
       <c r="O18">
         <v>50.75</v>
       </c>
-    </row>
-    <row r="19" spans="1:15">
+      <c r="P18">
+        <v>45.92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1395,8 +1446,11 @@
       <c r="O19">
         <v>47.43994140625</v>
       </c>
-    </row>
-    <row r="20" spans="1:15">
+      <c r="P19">
+        <v>52.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1442,8 +1496,11 @@
       <c r="O20">
         <v>57.14990234375</v>
       </c>
-    </row>
-    <row r="21" spans="1:15">
+      <c r="P20">
+        <v>53.93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1489,8 +1546,11 @@
       <c r="O21">
         <v>53.780029296875</v>
       </c>
-    </row>
-    <row r="22" spans="1:15">
+      <c r="P21">
+        <v>63.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1535,6 +1595,9 @@
       </c>
       <c r="O22" t="s">
         <v>21</v>
+      </c>
+      <c r="P22" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -600,7 +600,7 @@
         <v>57.8798828125</v>
       </c>
       <c r="P2">
-        <v>45.78</v>
+        <v>45.780029296875</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -650,7 +650,7 @@
         <v>69.4501953125</v>
       </c>
       <c r="P3">
-        <v>50.98</v>
+        <v>50.97998046875</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -700,7 +700,7 @@
         <v>78.4501953125</v>
       </c>
       <c r="P4">
-        <v>45.15</v>
+        <v>45.14990234375</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -750,7 +750,7 @@
         <v>55.139892578125</v>
       </c>
       <c r="P5">
-        <v>58.04</v>
+        <v>58.179931640625</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -800,7 +800,7 @@
         <v>53.25</v>
       </c>
       <c r="P6">
-        <v>39.12</v>
+        <v>39.1201171875</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -850,7 +850,7 @@
         <v>61.949951171875</v>
       </c>
       <c r="P7">
-        <v>60.17</v>
+        <v>60.169921875</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -900,7 +900,7 @@
         <v>70.14013671875</v>
       </c>
       <c r="P8">
-        <v>81.98</v>
+        <v>81.97998046875</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -950,7 +950,7 @@
         <v>67.83984375</v>
       </c>
       <c r="P9">
-        <v>64.2</v>
+        <v>64.2001953125</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1000,7 +1000,7 @@
         <v>58.43994140625</v>
       </c>
       <c r="P10">
-        <v>50.2</v>
+        <v>50.199951171875</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1050,7 +1050,7 @@
         <v>71.25</v>
       </c>
       <c r="P11">
-        <v>55.52</v>
+        <v>55.52001953125</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1100,7 +1100,7 @@
         <v>57.72998046875</v>
       </c>
       <c r="P12">
-        <v>55.9</v>
+        <v>55.89990234375</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1150,7 +1150,7 @@
         <v>66.080078125</v>
       </c>
       <c r="P13">
-        <v>49.62</v>
+        <v>49.6201171875</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1200,7 +1200,7 @@
         <v>49.280029296875</v>
       </c>
       <c r="P14">
-        <v>54.58</v>
+        <v>54.580078125</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1250,7 +1250,7 @@
         <v>66.0498046875</v>
       </c>
       <c r="P15">
-        <v>35.42</v>
+        <v>35.419921875</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1297,7 +1297,7 @@
         <v>31.6500244140625</v>
       </c>
       <c r="P16">
-        <v>31.34</v>
+        <v>32.93994140625</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1347,7 +1347,7 @@
         <v>30.030029296875</v>
       </c>
       <c r="P17">
-        <v>42.1</v>
+        <v>42.10009765625</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1397,7 +1397,7 @@
         <v>50.75</v>
       </c>
       <c r="P18">
-        <v>45.92</v>
+        <v>45.919921875</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1447,7 +1447,7 @@
         <v>47.43994140625</v>
       </c>
       <c r="P19">
-        <v>52.2</v>
+        <v>52.199951171875</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1497,7 +1497,7 @@
         <v>57.14990234375</v>
       </c>
       <c r="P20">
-        <v>53.93</v>
+        <v>53.929931640625</v>
       </c>
     </row>
     <row r="21" spans="1:16">

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -602,6 +602,9 @@
       <c r="P2">
         <v>45.780029296875</v>
       </c>
+      <c r="Q2">
+        <v>74.75</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -652,6 +655,9 @@
       <c r="P3">
         <v>50.97998046875</v>
       </c>
+      <c r="Q3">
+        <v>57.83</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -702,6 +708,9 @@
       <c r="P4">
         <v>45.14990234375</v>
       </c>
+      <c r="Q4">
+        <v>105.5</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -752,6 +761,9 @@
       <c r="P5">
         <v>58.179931640625</v>
       </c>
+      <c r="Q5">
+        <v>96.79000000000001</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -802,6 +814,9 @@
       <c r="P6">
         <v>39.1201171875</v>
       </c>
+      <c r="Q6">
+        <v>86.83</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
@@ -852,6 +867,9 @@
       <c r="P7">
         <v>60.169921875</v>
       </c>
+      <c r="Q7">
+        <v>72.28</v>
+      </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="1" t="s">
@@ -902,6 +920,9 @@
       <c r="P8">
         <v>81.97998046875</v>
       </c>
+      <c r="Q8">
+        <v>81.78</v>
+      </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="1" t="s">
@@ -952,6 +973,9 @@
       <c r="P9">
         <v>64.2001953125</v>
       </c>
+      <c r="Q9">
+        <v>74.7</v>
+      </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="1" t="s">
@@ -1002,6 +1026,9 @@
       <c r="P10">
         <v>50.199951171875</v>
       </c>
+      <c r="Q10">
+        <v>74.55</v>
+      </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="1" t="s">
@@ -1052,6 +1079,9 @@
       <c r="P11">
         <v>55.52001953125</v>
       </c>
+      <c r="Q11">
+        <v>69.15000000000001</v>
+      </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="1" t="s">
@@ -1102,6 +1132,9 @@
       <c r="P12">
         <v>55.89990234375</v>
       </c>
+      <c r="Q12">
+        <v>103.39</v>
+      </c>
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="1" t="s">
@@ -1152,6 +1185,9 @@
       <c r="P13">
         <v>49.6201171875</v>
       </c>
+      <c r="Q13">
+        <v>76.28</v>
+      </c>
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="1" t="s">
@@ -1202,6 +1238,9 @@
       <c r="P14">
         <v>54.580078125</v>
       </c>
+      <c r="Q14">
+        <v>68.58</v>
+      </c>
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="1" t="s">
@@ -1252,6 +1291,9 @@
       <c r="P15">
         <v>35.419921875</v>
       </c>
+      <c r="Q15">
+        <v>91.34999999999999</v>
+      </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
@@ -1299,8 +1341,11 @@
       <c r="P16">
         <v>32.93994140625</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16">
+        <v>48.94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -1349,8 +1394,11 @@
       <c r="P17">
         <v>42.10009765625</v>
       </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17">
+        <v>19.51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1399,8 +1447,11 @@
       <c r="P18">
         <v>45.919921875</v>
       </c>
-    </row>
-    <row r="19" spans="1:16">
+      <c r="Q18">
+        <v>63.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
@@ -1449,8 +1500,11 @@
       <c r="P19">
         <v>52.199951171875</v>
       </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="Q19">
+        <v>108.44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
@@ -1499,8 +1553,11 @@
       <c r="P20">
         <v>53.929931640625</v>
       </c>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20">
+        <v>79.2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
@@ -1549,8 +1606,11 @@
       <c r="P21">
         <v>63.75</v>
       </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21">
+        <v>73.08</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1598,6 +1658,9 @@
       </c>
       <c r="P22" t="s">
         <v>25</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -656,7 +656,7 @@
         <v>50.97998046875</v>
       </c>
       <c r="Q3">
-        <v>57.83</v>
+        <v>57.830078125</v>
       </c>
     </row>
     <row r="4" spans="1:20">
@@ -762,7 +762,7 @@
         <v>58.179931640625</v>
       </c>
       <c r="Q5">
-        <v>96.79000000000001</v>
+        <v>96.7900390625</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -815,7 +815,7 @@
         <v>39.1201171875</v>
       </c>
       <c r="Q6">
-        <v>86.83</v>
+        <v>86.830078125</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -868,7 +868,7 @@
         <v>60.169921875</v>
       </c>
       <c r="Q7">
-        <v>72.28</v>
+        <v>72.27978515625</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -921,7 +921,7 @@
         <v>81.97998046875</v>
       </c>
       <c r="Q8">
-        <v>81.78</v>
+        <v>81.77978515625</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -974,7 +974,7 @@
         <v>64.2001953125</v>
       </c>
       <c r="Q9">
-        <v>74.7</v>
+        <v>74.7001953125</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1027,7 +1027,7 @@
         <v>50.199951171875</v>
       </c>
       <c r="Q10">
-        <v>74.55</v>
+        <v>74.5498046875</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1080,7 +1080,7 @@
         <v>55.52001953125</v>
       </c>
       <c r="Q11">
-        <v>69.15000000000001</v>
+        <v>69.14990234375</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1133,7 +1133,7 @@
         <v>55.89990234375</v>
       </c>
       <c r="Q12">
-        <v>103.39</v>
+        <v>103.39013671875</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1186,7 +1186,7 @@
         <v>49.6201171875</v>
       </c>
       <c r="Q13">
-        <v>76.28</v>
+        <v>76.27978515625</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1239,7 +1239,7 @@
         <v>54.580078125</v>
       </c>
       <c r="Q14">
-        <v>68.58</v>
+        <v>68.580078125</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1292,7 +1292,7 @@
         <v>35.419921875</v>
       </c>
       <c r="Q15">
-        <v>91.34999999999999</v>
+        <v>91.35009765625</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -1342,7 +1342,7 @@
         <v>32.93994140625</v>
       </c>
       <c r="Q16">
-        <v>48.94</v>
+        <v>48.93994140625</v>
       </c>
     </row>
     <row r="17" spans="1:17">
@@ -1395,7 +1395,7 @@
         <v>42.10009765625</v>
       </c>
       <c r="Q17">
-        <v>19.51</v>
+        <v>19.510009765625</v>
       </c>
     </row>
     <row r="18" spans="1:17">
@@ -1448,7 +1448,7 @@
         <v>45.919921875</v>
       </c>
       <c r="Q18">
-        <v>63.6</v>
+        <v>63.60009765625</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -1501,7 +1501,7 @@
         <v>52.199951171875</v>
       </c>
       <c r="Q19">
-        <v>108.44</v>
+        <v>108.43994140625</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -1554,7 +1554,7 @@
         <v>53.929931640625</v>
       </c>
       <c r="Q20">
-        <v>79.2</v>
+        <v>79.2001953125</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -1607,7 +1607,7 @@
         <v>63.75</v>
       </c>
       <c r="Q21">
-        <v>73.08</v>
+        <v>73.080078125</v>
       </c>
     </row>
     <row r="22" spans="1:17">

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -88,49 +88,49 @@
     <t>Esquadrão Gazembrino</t>
   </si>
   <si>
+    <t>GaúchoDaFronteira F.C</t>
+  </si>
+  <si>
+    <t>GE Xavanchesteer</t>
+  </si>
+  <si>
+    <t>GrioTeam</t>
+  </si>
+  <si>
+    <t>Grêmio_Campeão_LA_27</t>
+  </si>
+  <si>
+    <t>La Primeira Patada Es Nuestra</t>
+  </si>
+  <si>
+    <t>lsauer fc</t>
+  </si>
+  <si>
+    <t>Medonho´s F.C.</t>
+  </si>
+  <si>
+    <t>Pepe Leal FC</t>
+  </si>
+  <si>
+    <t>Pontaç0 F.C.</t>
+  </si>
+  <si>
+    <t>SC 100 Sono</t>
+  </si>
+  <si>
+    <t>SC ÉoINTER!</t>
+  </si>
+  <si>
+    <t>Texas Club 2026</t>
+  </si>
+  <si>
     <t>FBC Colorado</t>
   </si>
   <si>
-    <t>GaúchoDaFronteira F.C</t>
-  </si>
-  <si>
-    <t>GE Xavanchesteer</t>
-  </si>
-  <si>
-    <t>GrioTeam</t>
-  </si>
-  <si>
-    <t>Grêmio_Campeão_LA_27</t>
-  </si>
-  <si>
     <t>JV5 Tricolor Gaúcho</t>
   </si>
   <si>
-    <t>La Primeira Patada Es Nuestra</t>
-  </si>
-  <si>
-    <t>lsauer fc</t>
-  </si>
-  <si>
-    <t>Medonho´s F.C.</t>
-  </si>
-  <si>
     <t>NHU PORÃ SAF.</t>
-  </si>
-  <si>
-    <t>Pepe Leal FC</t>
-  </si>
-  <si>
-    <t>Pontaç0 F.C.</t>
-  </si>
-  <si>
-    <t>SC 100 Sono</t>
-  </si>
-  <si>
-    <t>SC ÉoINTER!</t>
-  </si>
-  <si>
-    <t>Texas Club 2026</t>
   </si>
   <si>
     <t>Lider_Rodada</t>
@@ -605,6 +605,9 @@
       <c r="Q2">
         <v>74.75</v>
       </c>
+      <c r="R2">
+        <v>68.02001953125</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -658,6 +661,9 @@
       <c r="Q3">
         <v>57.830078125</v>
       </c>
+      <c r="R3">
+        <v>76.8701171875</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -711,6 +717,9 @@
       <c r="Q4">
         <v>105.5</v>
       </c>
+      <c r="R4">
+        <v>85.919921875</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -764,6 +773,9 @@
       <c r="Q5">
         <v>96.7900390625</v>
       </c>
+      <c r="R5">
+        <v>61.419921875</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -817,58 +829,64 @@
       <c r="Q6">
         <v>86.830078125</v>
       </c>
+      <c r="R6">
+        <v>61.77001953125</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B7">
-        <v>53.659912109375</v>
+        <v>71.9599609375</v>
       </c>
       <c r="C7">
-        <v>81.47998046875</v>
+        <v>66.68017578125</v>
       </c>
       <c r="D7">
-        <v>79.259765625</v>
+        <v>42.14990234375</v>
       </c>
       <c r="E7">
-        <v>86.43017578125</v>
+        <v>30.800048828125</v>
       </c>
       <c r="F7">
-        <v>86.419921875</v>
+        <v>52.5400390625</v>
       </c>
       <c r="G7">
-        <v>47.389892578125</v>
+        <v>34.550048828125</v>
       </c>
       <c r="H7">
-        <v>67.27001953125</v>
+        <v>61.5</v>
       </c>
       <c r="I7">
-        <v>75.75</v>
+        <v>77</v>
       </c>
       <c r="J7">
-        <v>85.9599609375</v>
+        <v>68.68017578125</v>
       </c>
       <c r="K7">
-        <v>39.469970703125</v>
+        <v>19.4000244140625</v>
       </c>
       <c r="L7">
-        <v>85.16015625</v>
+        <v>95.259765625</v>
       </c>
       <c r="M7">
-        <v>81.4501953125</v>
+        <v>72.10009765625</v>
       </c>
       <c r="N7">
-        <v>113.2900390625</v>
+        <v>118.43994140625</v>
       </c>
       <c r="O7">
-        <v>61.949951171875</v>
+        <v>70.14013671875</v>
       </c>
       <c r="P7">
-        <v>60.169921875</v>
+        <v>81.97998046875</v>
       </c>
       <c r="Q7">
-        <v>72.27978515625</v>
+        <v>81.77978515625</v>
+      </c>
+      <c r="R7">
+        <v>76.31982421875</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -876,52 +894,55 @@
         <v>25</v>
       </c>
       <c r="B8">
-        <v>71.9599609375</v>
+        <v>56.050048828125</v>
       </c>
       <c r="C8">
-        <v>66.68017578125</v>
+        <v>70.43994140625</v>
       </c>
       <c r="D8">
-        <v>42.14990234375</v>
+        <v>71.64013671875</v>
       </c>
       <c r="E8">
-        <v>30.800048828125</v>
+        <v>56.360107421875</v>
       </c>
       <c r="F8">
-        <v>52.5400390625</v>
+        <v>88.240234375</v>
       </c>
       <c r="G8">
-        <v>34.550048828125</v>
+        <v>61.989990234375</v>
       </c>
       <c r="H8">
-        <v>61.5</v>
+        <v>48.469970703125</v>
       </c>
       <c r="I8">
-        <v>77</v>
+        <v>82.85009765625</v>
       </c>
       <c r="J8">
-        <v>68.68017578125</v>
+        <v>85.52978515625</v>
       </c>
       <c r="K8">
-        <v>19.4000244140625</v>
+        <v>55.179931640625</v>
       </c>
       <c r="L8">
-        <v>95.259765625</v>
+        <v>93.68017578125</v>
       </c>
       <c r="M8">
-        <v>72.10009765625</v>
+        <v>75</v>
       </c>
       <c r="N8">
-        <v>118.43994140625</v>
+        <v>108.39013671875</v>
       </c>
       <c r="O8">
-        <v>70.14013671875</v>
+        <v>67.83984375</v>
       </c>
       <c r="P8">
-        <v>81.97998046875</v>
+        <v>64.2001953125</v>
       </c>
       <c r="Q8">
-        <v>81.77978515625</v>
+        <v>74.7001953125</v>
+      </c>
+      <c r="R8">
+        <v>69.6201171875</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -929,52 +950,55 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>56.050048828125</v>
+        <v>61.56005859375</v>
       </c>
       <c r="C9">
-        <v>70.43994140625</v>
+        <v>83.47998046875</v>
       </c>
       <c r="D9">
-        <v>71.64013671875</v>
+        <v>90.4599609375</v>
       </c>
       <c r="E9">
-        <v>56.360107421875</v>
+        <v>76.06005859375</v>
       </c>
       <c r="F9">
-        <v>88.240234375</v>
+        <v>41.169921875</v>
       </c>
       <c r="G9">
-        <v>61.989990234375</v>
+        <v>71.009765625</v>
       </c>
       <c r="H9">
-        <v>48.469970703125</v>
+        <v>65.47021484375</v>
       </c>
       <c r="I9">
-        <v>82.85009765625</v>
+        <v>34.110107421875</v>
       </c>
       <c r="J9">
-        <v>85.52978515625</v>
+        <v>70.740234375</v>
       </c>
       <c r="K9">
-        <v>55.179931640625</v>
+        <v>53.280029296875</v>
       </c>
       <c r="L9">
-        <v>93.68017578125</v>
+        <v>96.4599609375</v>
       </c>
       <c r="M9">
-        <v>75</v>
+        <v>64.919921875</v>
       </c>
       <c r="N9">
-        <v>108.39013671875</v>
+        <v>118.240234375</v>
       </c>
       <c r="O9">
-        <v>67.83984375</v>
+        <v>58.43994140625</v>
       </c>
       <c r="P9">
-        <v>64.2001953125</v>
+        <v>50.199951171875</v>
       </c>
       <c r="Q9">
-        <v>74.7001953125</v>
+        <v>74.5498046875</v>
+      </c>
+      <c r="R9">
+        <v>82.919921875</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -982,52 +1006,55 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>61.56005859375</v>
+        <v>54.050048828125</v>
       </c>
       <c r="C10">
-        <v>83.47998046875</v>
+        <v>85.7001953125</v>
       </c>
       <c r="D10">
-        <v>90.4599609375</v>
+        <v>65.66015625</v>
       </c>
       <c r="E10">
-        <v>76.06005859375</v>
+        <v>49.449951171875</v>
       </c>
       <c r="F10">
-        <v>41.169921875</v>
+        <v>87.72021484375</v>
       </c>
       <c r="G10">
-        <v>71.009765625</v>
+        <v>77.7998046875</v>
       </c>
       <c r="H10">
-        <v>65.47021484375</v>
+        <v>57.93994140625</v>
       </c>
       <c r="I10">
-        <v>34.110107421875</v>
+        <v>42.89990234375</v>
       </c>
       <c r="J10">
-        <v>70.740234375</v>
+        <v>97.68017578125</v>
       </c>
       <c r="K10">
-        <v>53.280029296875</v>
+        <v>65.3701171875</v>
       </c>
       <c r="L10">
-        <v>96.4599609375</v>
+        <v>82.4599609375</v>
       </c>
       <c r="M10">
-        <v>64.919921875</v>
+        <v>69.89990234375</v>
       </c>
       <c r="N10">
-        <v>118.240234375</v>
+        <v>108.58984375</v>
       </c>
       <c r="O10">
-        <v>58.43994140625</v>
+        <v>71.25</v>
       </c>
       <c r="P10">
-        <v>50.199951171875</v>
+        <v>55.52001953125</v>
       </c>
       <c r="Q10">
-        <v>74.5498046875</v>
+        <v>69.14990234375</v>
+      </c>
+      <c r="R10">
+        <v>76.6201171875</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1035,52 +1062,55 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>54.050048828125</v>
+        <v>55.659912109375</v>
       </c>
       <c r="C11">
-        <v>85.7001953125</v>
+        <v>73.60009765625</v>
       </c>
       <c r="D11">
-        <v>65.66015625</v>
+        <v>100.06005859375</v>
       </c>
       <c r="E11">
-        <v>49.449951171875</v>
+        <v>62.75</v>
       </c>
       <c r="F11">
-        <v>87.72021484375</v>
+        <v>77.22021484375</v>
       </c>
       <c r="G11">
-        <v>77.7998046875</v>
+        <v>88.2099609375</v>
       </c>
       <c r="H11">
-        <v>57.93994140625</v>
+        <v>61.110107421875</v>
       </c>
       <c r="I11">
-        <v>42.89990234375</v>
+        <v>82.81982421875</v>
       </c>
       <c r="J11">
-        <v>97.68017578125</v>
+        <v>85.93994140625</v>
       </c>
       <c r="K11">
-        <v>65.3701171875</v>
+        <v>43.590087890625</v>
       </c>
       <c r="L11">
-        <v>82.4599609375</v>
+        <v>86.9599609375</v>
       </c>
       <c r="M11">
-        <v>69.89990234375</v>
+        <v>101.25</v>
       </c>
       <c r="N11">
-        <v>108.58984375</v>
+        <v>102.990234375</v>
       </c>
       <c r="O11">
-        <v>71.25</v>
+        <v>66.080078125</v>
       </c>
       <c r="P11">
-        <v>55.52001953125</v>
+        <v>49.6201171875</v>
       </c>
       <c r="Q11">
-        <v>69.14990234375</v>
+        <v>76.27978515625</v>
+      </c>
+      <c r="R11">
+        <v>58.820068359375</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1088,52 +1118,55 @@
         <v>29</v>
       </c>
       <c r="B12">
-        <v>47.860107421875</v>
+        <v>62.56005859375</v>
       </c>
       <c r="C12">
-        <v>72.18017578125</v>
+        <v>96.47998046875</v>
       </c>
       <c r="D12">
-        <v>97.39990234375</v>
+        <v>87.4599609375</v>
       </c>
       <c r="E12">
-        <v>81.64990234375</v>
+        <v>81.43017578125</v>
       </c>
       <c r="F12">
-        <v>84.81982421875</v>
+        <v>85.669921875</v>
       </c>
       <c r="G12">
-        <v>62.010009765625</v>
+        <v>58.610107421875</v>
       </c>
       <c r="H12">
-        <v>77.06982421875</v>
+        <v>81.56982421875</v>
       </c>
       <c r="I12">
-        <v>80.0498046875</v>
+        <v>73.35009765625</v>
       </c>
       <c r="J12">
-        <v>59.010009765625</v>
+        <v>104.68017578125</v>
       </c>
       <c r="K12">
-        <v>60.169921875</v>
+        <v>66.89013671875</v>
       </c>
       <c r="L12">
-        <v>82.81005859375</v>
+        <v>90.4599609375</v>
       </c>
       <c r="M12">
-        <v>77.35009765625</v>
+        <v>84.39990234375</v>
       </c>
       <c r="N12">
-        <v>115.43994140625</v>
+        <v>108.58984375</v>
       </c>
       <c r="O12">
-        <v>57.72998046875</v>
+        <v>49.280029296875</v>
       </c>
       <c r="P12">
-        <v>55.89990234375</v>
+        <v>54.580078125</v>
       </c>
       <c r="Q12">
-        <v>103.39013671875</v>
+        <v>68.580078125</v>
+      </c>
+      <c r="R12">
+        <v>70.81982421875</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1144,49 +1177,52 @@
         <v>55.659912109375</v>
       </c>
       <c r="C13">
-        <v>73.60009765625</v>
+        <v>55.780029296875</v>
       </c>
       <c r="D13">
-        <v>100.06005859375</v>
+        <v>88.93994140625</v>
       </c>
       <c r="E13">
-        <v>62.75</v>
+        <v>59.409912109375</v>
       </c>
       <c r="F13">
-        <v>77.22021484375</v>
+        <v>84.6201171875</v>
       </c>
       <c r="G13">
-        <v>88.2099609375</v>
+        <v>75.81005859375</v>
       </c>
       <c r="H13">
-        <v>61.110107421875</v>
+        <v>83.22021484375</v>
       </c>
       <c r="I13">
-        <v>82.81982421875</v>
+        <v>85.64990234375</v>
       </c>
       <c r="J13">
+        <v>66.93994140625</v>
+      </c>
+      <c r="K13">
+        <v>58.949951171875</v>
+      </c>
+      <c r="L13">
+        <v>92.66015625</v>
+      </c>
+      <c r="M13">
+        <v>76.7998046875</v>
+      </c>
+      <c r="N13">
         <v>85.93994140625</v>
       </c>
-      <c r="K13">
-        <v>43.590087890625</v>
-      </c>
-      <c r="L13">
-        <v>86.9599609375</v>
-      </c>
-      <c r="M13">
-        <v>101.25</v>
-      </c>
-      <c r="N13">
-        <v>102.990234375</v>
-      </c>
       <c r="O13">
-        <v>66.080078125</v>
+        <v>66.0498046875</v>
       </c>
       <c r="P13">
-        <v>49.6201171875</v>
+        <v>35.419921875</v>
       </c>
       <c r="Q13">
-        <v>76.27978515625</v>
+        <v>91.35009765625</v>
+      </c>
+      <c r="R13">
+        <v>63.60009765625</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1194,52 +1230,55 @@
         <v>31</v>
       </c>
       <c r="B14">
-        <v>62.56005859375</v>
+        <v>60.60009765625</v>
       </c>
       <c r="C14">
-        <v>96.47998046875</v>
+        <v>75.8798828125</v>
       </c>
       <c r="D14">
-        <v>87.4599609375</v>
+        <v>87.39013671875</v>
       </c>
       <c r="E14">
-        <v>81.43017578125</v>
+        <v>42.56005859375</v>
       </c>
       <c r="F14">
-        <v>85.669921875</v>
+        <v>49.77001953125</v>
       </c>
       <c r="G14">
-        <v>58.610107421875</v>
+        <v>55.3798828125</v>
       </c>
       <c r="H14">
-        <v>81.56982421875</v>
+        <v>61.8701171875</v>
       </c>
       <c r="I14">
-        <v>73.35009765625</v>
+        <v>70.5400390625</v>
       </c>
       <c r="J14">
-        <v>104.68017578125</v>
+        <v>39.699951171875</v>
       </c>
       <c r="K14">
-        <v>66.89013671875</v>
+        <v>31.75</v>
       </c>
       <c r="L14">
-        <v>90.4599609375</v>
+        <v>51.530029296875</v>
       </c>
       <c r="M14">
-        <v>84.39990234375</v>
+        <v>35.2900390625</v>
       </c>
       <c r="N14">
-        <v>108.58984375</v>
+        <v>54.830078125</v>
       </c>
       <c r="O14">
-        <v>49.280029296875</v>
+        <v>30.030029296875</v>
       </c>
       <c r="P14">
-        <v>54.580078125</v>
+        <v>42.10009765625</v>
       </c>
       <c r="Q14">
-        <v>68.580078125</v>
+        <v>19.510009765625</v>
+      </c>
+      <c r="R14">
+        <v>52.949951171875</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1247,370 +1286,391 @@
         <v>32</v>
       </c>
       <c r="B15">
-        <v>55.659912109375</v>
+        <v>61.159912109375</v>
       </c>
       <c r="C15">
-        <v>55.780029296875</v>
+        <v>71.18017578125</v>
       </c>
       <c r="D15">
-        <v>88.93994140625</v>
+        <v>73.06005859375</v>
       </c>
       <c r="E15">
-        <v>59.409912109375</v>
+        <v>42.56005859375</v>
       </c>
       <c r="F15">
-        <v>84.6201171875</v>
+        <v>70.85986328125</v>
       </c>
       <c r="G15">
-        <v>75.81005859375</v>
+        <v>67.58984375</v>
       </c>
       <c r="H15">
-        <v>83.22021484375</v>
+        <v>71.77001953125</v>
       </c>
       <c r="I15">
-        <v>85.64990234375</v>
+        <v>68.25</v>
       </c>
       <c r="J15">
-        <v>66.93994140625</v>
+        <v>80.33984375</v>
       </c>
       <c r="K15">
-        <v>58.949951171875</v>
+        <v>60.050048828125</v>
       </c>
       <c r="L15">
-        <v>92.66015625</v>
+        <v>89.66015625</v>
       </c>
       <c r="M15">
-        <v>76.7998046875</v>
+        <v>81.9501953125</v>
       </c>
       <c r="N15">
-        <v>85.93994140625</v>
+        <v>113.18994140625</v>
       </c>
       <c r="O15">
-        <v>66.0498046875</v>
+        <v>50.75</v>
       </c>
       <c r="P15">
-        <v>35.419921875</v>
+        <v>45.919921875</v>
       </c>
       <c r="Q15">
-        <v>91.35009765625</v>
+        <v>63.60009765625</v>
+      </c>
+      <c r="R15">
+        <v>81.9501953125</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="B16">
+        <v>67.16015625</v>
+      </c>
       <c r="C16">
-        <v>95.41015625</v>
+        <v>86.4501953125</v>
       </c>
       <c r="D16">
-        <v>57.0400390625</v>
+        <v>64.35986328125</v>
       </c>
       <c r="E16">
-        <v>72.240234375</v>
+        <v>61.1298828125</v>
       </c>
       <c r="F16">
-        <v>69.77001953125</v>
+        <v>72.759765625</v>
       </c>
       <c r="G16">
-        <v>47.989990234375</v>
+        <v>61.199951171875</v>
       </c>
       <c r="H16">
-        <v>46.550048828125</v>
+        <v>69.60009765625</v>
       </c>
       <c r="I16">
-        <v>59.909912109375</v>
+        <v>67.14990234375</v>
       </c>
       <c r="J16">
-        <v>70.47998046875</v>
+        <v>62.89990234375</v>
       </c>
       <c r="K16">
-        <v>66.580078125</v>
+        <v>43.25</v>
       </c>
       <c r="L16">
-        <v>29.8499755859375</v>
+        <v>81.8798828125</v>
       </c>
       <c r="M16">
-        <v>57.10009765625</v>
+        <v>41.570068359375</v>
       </c>
       <c r="N16">
-        <v>31.050048828125</v>
+        <v>96.83984375</v>
       </c>
       <c r="O16">
-        <v>31.6500244140625</v>
+        <v>47.43994140625</v>
       </c>
       <c r="P16">
-        <v>32.93994140625</v>
+        <v>52.199951171875</v>
       </c>
       <c r="Q16">
-        <v>48.93994140625</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17">
+        <v>108.43994140625</v>
+      </c>
+      <c r="R16">
+        <v>68.22021484375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B17">
-        <v>60.60009765625</v>
+        <v>54.89990234375</v>
       </c>
       <c r="C17">
-        <v>75.8798828125</v>
+        <v>77.60009765625</v>
       </c>
       <c r="D17">
-        <v>87.39013671875</v>
+        <v>78.259765625</v>
       </c>
       <c r="E17">
-        <v>42.56005859375</v>
+        <v>45.550048828125</v>
       </c>
       <c r="F17">
-        <v>49.77001953125</v>
+        <v>77.6201171875</v>
       </c>
       <c r="G17">
-        <v>55.3798828125</v>
+        <v>79.009765625</v>
       </c>
       <c r="H17">
-        <v>61.8701171875</v>
+        <v>65.47021484375</v>
       </c>
       <c r="I17">
-        <v>70.5400390625</v>
+        <v>80.85009765625</v>
       </c>
       <c r="J17">
-        <v>39.699951171875</v>
+        <v>94.27978515625</v>
       </c>
       <c r="K17">
-        <v>31.75</v>
+        <v>70.77001953125</v>
       </c>
       <c r="L17">
-        <v>51.530029296875</v>
+        <v>98.56005859375</v>
       </c>
       <c r="M17">
-        <v>35.2900390625</v>
+        <v>83.5</v>
       </c>
       <c r="N17">
-        <v>54.830078125</v>
+        <v>114.08984375</v>
       </c>
       <c r="O17">
-        <v>30.030029296875</v>
+        <v>57.14990234375</v>
       </c>
       <c r="P17">
-        <v>42.10009765625</v>
+        <v>53.929931640625</v>
       </c>
       <c r="Q17">
-        <v>19.510009765625</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17">
+        <v>79.2001953125</v>
+      </c>
+      <c r="R17">
+        <v>66.31982421875</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B18">
-        <v>61.159912109375</v>
+        <v>68.06005859375</v>
       </c>
       <c r="C18">
-        <v>71.18017578125</v>
+        <v>82.18017578125</v>
       </c>
       <c r="D18">
-        <v>73.06005859375</v>
+        <v>105.759765625</v>
       </c>
       <c r="E18">
-        <v>42.56005859375</v>
+        <v>65.14990234375</v>
       </c>
       <c r="F18">
-        <v>70.85986328125</v>
+        <v>93.02001953125</v>
       </c>
       <c r="G18">
-        <v>67.58984375</v>
+        <v>83</v>
       </c>
       <c r="H18">
-        <v>71.77001953125</v>
+        <v>76.97021484375</v>
       </c>
       <c r="I18">
-        <v>68.25</v>
+        <v>76.4501953125</v>
       </c>
       <c r="J18">
-        <v>80.33984375</v>
+        <v>85.85009765625</v>
       </c>
       <c r="K18">
-        <v>60.050048828125</v>
+        <v>58.090087890625</v>
       </c>
       <c r="L18">
-        <v>89.66015625</v>
+        <v>88.759765625</v>
       </c>
       <c r="M18">
-        <v>81.9501953125</v>
+        <v>86.66015625</v>
       </c>
       <c r="N18">
-        <v>113.18994140625</v>
+        <v>106.39013671875</v>
       </c>
       <c r="O18">
-        <v>50.75</v>
+        <v>53.780029296875</v>
       </c>
       <c r="P18">
-        <v>45.919921875</v>
+        <v>63.75</v>
       </c>
       <c r="Q18">
-        <v>63.60009765625</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17">
+        <v>73.080078125</v>
+      </c>
+      <c r="R18">
+        <v>65.6201171875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B19">
-        <v>67.16015625</v>
+        <v>53.659912109375</v>
       </c>
       <c r="C19">
-        <v>86.4501953125</v>
+        <v>81.47998046875</v>
       </c>
       <c r="D19">
-        <v>64.35986328125</v>
+        <v>79.259765625</v>
       </c>
       <c r="E19">
-        <v>61.1298828125</v>
+        <v>86.43017578125</v>
       </c>
       <c r="F19">
-        <v>72.759765625</v>
+        <v>86.419921875</v>
       </c>
       <c r="G19">
-        <v>61.199951171875</v>
+        <v>47.389892578125</v>
       </c>
       <c r="H19">
-        <v>69.60009765625</v>
+        <v>67.27001953125</v>
       </c>
       <c r="I19">
-        <v>67.14990234375</v>
+        <v>75.75</v>
       </c>
       <c r="J19">
-        <v>62.89990234375</v>
+        <v>85.9599609375</v>
       </c>
       <c r="K19">
-        <v>43.25</v>
+        <v>39.469970703125</v>
       </c>
       <c r="L19">
-        <v>81.8798828125</v>
+        <v>85.16015625</v>
       </c>
       <c r="M19">
-        <v>41.570068359375</v>
+        <v>81.4501953125</v>
       </c>
       <c r="N19">
-        <v>96.83984375</v>
+        <v>113.2900390625</v>
       </c>
       <c r="O19">
-        <v>47.43994140625</v>
+        <v>61.949951171875</v>
       </c>
       <c r="P19">
-        <v>52.199951171875</v>
+        <v>60.169921875</v>
       </c>
       <c r="Q19">
-        <v>108.43994140625</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17">
+        <v>72.27978515625</v>
+      </c>
+      <c r="R19">
+        <v>65.31982421875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B20">
-        <v>54.89990234375</v>
+        <v>47.860107421875</v>
       </c>
       <c r="C20">
-        <v>77.60009765625</v>
+        <v>72.18017578125</v>
       </c>
       <c r="D20">
-        <v>78.259765625</v>
+        <v>97.39990234375</v>
       </c>
       <c r="E20">
-        <v>45.550048828125</v>
+        <v>81.64990234375</v>
       </c>
       <c r="F20">
-        <v>77.6201171875</v>
+        <v>84.81982421875</v>
       </c>
       <c r="G20">
-        <v>79.009765625</v>
+        <v>62.010009765625</v>
       </c>
       <c r="H20">
-        <v>65.47021484375</v>
+        <v>77.06982421875</v>
       </c>
       <c r="I20">
-        <v>80.85009765625</v>
+        <v>80.0498046875</v>
       </c>
       <c r="J20">
-        <v>94.27978515625</v>
+        <v>59.010009765625</v>
       </c>
       <c r="K20">
-        <v>70.77001953125</v>
+        <v>60.169921875</v>
       </c>
       <c r="L20">
-        <v>98.56005859375</v>
+        <v>82.81005859375</v>
       </c>
       <c r="M20">
-        <v>83.5</v>
+        <v>77.35009765625</v>
       </c>
       <c r="N20">
-        <v>114.08984375</v>
+        <v>115.43994140625</v>
       </c>
       <c r="O20">
-        <v>57.14990234375</v>
+        <v>57.72998046875</v>
       </c>
       <c r="P20">
-        <v>53.929931640625</v>
+        <v>55.89990234375</v>
       </c>
       <c r="Q20">
-        <v>79.2001953125</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17">
+        <v>103.39013671875</v>
+      </c>
+      <c r="R20">
+        <v>60.1201171875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B21">
-        <v>68.06005859375</v>
-      </c>
       <c r="C21">
-        <v>82.18017578125</v>
+        <v>95.41015625</v>
       </c>
       <c r="D21">
-        <v>105.759765625</v>
+        <v>57.0400390625</v>
       </c>
       <c r="E21">
-        <v>65.14990234375</v>
+        <v>72.240234375</v>
       </c>
       <c r="F21">
-        <v>93.02001953125</v>
+        <v>69.77001953125</v>
       </c>
       <c r="G21">
-        <v>83</v>
+        <v>47.989990234375</v>
       </c>
       <c r="H21">
-        <v>76.97021484375</v>
+        <v>46.550048828125</v>
       </c>
       <c r="I21">
-        <v>76.4501953125</v>
+        <v>59.909912109375</v>
       </c>
       <c r="J21">
-        <v>85.85009765625</v>
+        <v>70.47998046875</v>
       </c>
       <c r="K21">
-        <v>58.090087890625</v>
+        <v>66.580078125</v>
       </c>
       <c r="L21">
-        <v>88.759765625</v>
+        <v>29.8499755859375</v>
       </c>
       <c r="M21">
-        <v>86.66015625</v>
+        <v>57.10009765625</v>
       </c>
       <c r="N21">
-        <v>106.39013671875</v>
+        <v>31.050048828125</v>
       </c>
       <c r="O21">
-        <v>53.780029296875</v>
+        <v>31.6500244140625</v>
       </c>
       <c r="P21">
-        <v>63.75</v>
+        <v>32.93994140625</v>
       </c>
       <c r="Q21">
-        <v>73.080078125</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17">
+        <v>48.93994140625</v>
+      </c>
+      <c r="R21">
+        <v>75.419921875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1630,37 +1690,40 @@
         <v>23</v>
       </c>
       <c r="G22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H22" t="s">
         <v>23</v>
       </c>
       <c r="I22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J22" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="L22" t="s">
         <v>19</v>
       </c>
       <c r="M22" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="N22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O22" t="s">
         <v>21</v>
       </c>
       <c r="P22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q22" t="s">
-        <v>36</v>
+        <v>33</v>
+      </c>
+      <c r="R22" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
+++ b/pontos_corridos/datasets_pontos_corridos/Pontuacoes_Liga_1_Turno_Completa.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
   <si>
     <t>Rodada 1</t>
   </si>
@@ -88,6 +88,9 @@
     <t>Esquadrão Gazembrino</t>
   </si>
   <si>
+    <t>FBC Colorado</t>
+  </si>
+  <si>
     <t>GaúchoDaFronteira F.C</t>
   </si>
   <si>
@@ -100,6 +103,9 @@
     <t>Grêmio_Campeão_LA_27</t>
   </si>
   <si>
+    <t>JV5 Tricolor Gaúcho</t>
+  </si>
+  <si>
     <t>La Primeira Patada Es Nuestra</t>
   </si>
   <si>
@@ -109,6 +115,9 @@
     <t>Medonho´s F.C.</t>
   </si>
   <si>
+    <t>NHU PORÃ SAF.</t>
+  </si>
+  <si>
     <t>Pepe Leal FC</t>
   </si>
   <si>
@@ -122,15 +131,6 @@
   </si>
   <si>
     <t>Texas Club 2026</t>
-  </si>
-  <si>
-    <t>FBC Colorado</t>
-  </si>
-  <si>
-    <t>JV5 Tricolor Gaúcho</t>
-  </si>
-  <si>
-    <t>NHU PORÃ SAF.</t>
   </si>
   <si>
     <t>Lider_Rodada</t>
@@ -608,6 +608,9 @@
       <c r="R2">
         <v>68.02001953125</v>
       </c>
+      <c r="S2">
+        <v>112.25</v>
+      </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="1" t="s">
@@ -664,6 +667,9 @@
       <c r="R3">
         <v>76.8701171875</v>
       </c>
+      <c r="S3">
+        <v>103.0498046875</v>
+      </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="1" t="s">
@@ -720,6 +726,9 @@
       <c r="R4">
         <v>85.919921875</v>
       </c>
+      <c r="S4">
+        <v>121.85009765625</v>
+      </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="1" t="s">
@@ -776,6 +785,9 @@
       <c r="R5">
         <v>61.419921875</v>
       </c>
+      <c r="S5">
+        <v>105.60009765625</v>
+      </c>
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="1" t="s">
@@ -832,61 +844,67 @@
       <c r="R6">
         <v>61.77001953125</v>
       </c>
+      <c r="S6">
+        <v>95.39990234375</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B7">
-        <v>71.9599609375</v>
+        <v>53.659912109375</v>
       </c>
       <c r="C7">
-        <v>66.68017578125</v>
+        <v>81.47998046875</v>
       </c>
       <c r="D7">
-        <v>42.14990234375</v>
+        <v>79.259765625</v>
       </c>
       <c r="E7">
-        <v>30.800048828125</v>
+        <v>86.43017578125</v>
       </c>
       <c r="F7">
-        <v>52.5400390625</v>
+        <v>86.419921875</v>
       </c>
       <c r="G7">
-        <v>34.550048828125</v>
+        <v>47.389892578125</v>
       </c>
       <c r="H7">
-        <v>61.5</v>
+        <v>67.27001953125</v>
       </c>
       <c r="I7">
-        <v>77</v>
+        <v>75.75</v>
       </c>
       <c r="J7">
-        <v>68.68017578125</v>
+        <v>85.9599609375</v>
       </c>
       <c r="K7">
-        <v>19.4000244140625</v>
+        <v>39.469970703125</v>
       </c>
       <c r="L7">
-        <v>95.259765625</v>
+        <v>85.16015625</v>
       </c>
       <c r="M7">
-        <v>72.10009765625</v>
+        <v>81.4501953125</v>
       </c>
       <c r="N7">
-        <v>118.43994140625</v>
+        <v>113.2900390625</v>
       </c>
       <c r="O7">
-        <v>70.14013671875</v>
+        <v>61.949951171875</v>
       </c>
       <c r="P7">
-        <v>81.97998046875</v>
+        <v>60.169921875</v>
       </c>
       <c r="Q7">
-        <v>81.77978515625</v>
+        <v>72.27978515625</v>
       </c>
       <c r="R7">
-        <v>76.31982421875</v>
+        <v>65.31982421875</v>
+      </c>
+      <c r="S7">
+        <v>106.64990234375</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -894,55 +912,58 @@
         <v>25</v>
       </c>
       <c r="B8">
-        <v>56.050048828125</v>
+        <v>71.9599609375</v>
       </c>
       <c r="C8">
-        <v>70.43994140625</v>
+        <v>66.68017578125</v>
       </c>
       <c r="D8">
-        <v>71.64013671875</v>
+        <v>42.14990234375</v>
       </c>
       <c r="E8">
-        <v>56.360107421875</v>
+        <v>30.800048828125</v>
       </c>
       <c r="F8">
-        <v>88.240234375</v>
+        <v>52.5400390625</v>
       </c>
       <c r="G8">
-        <v>61.989990234375</v>
+        <v>34.550048828125</v>
       </c>
       <c r="H8">
-        <v>48.469970703125</v>
+        <v>61.5</v>
       </c>
       <c r="I8">
-        <v>82.85009765625</v>
+        <v>77</v>
       </c>
       <c r="J8">
-        <v>85.52978515625</v>
+        <v>68.68017578125</v>
       </c>
       <c r="K8">
-        <v>55.179931640625</v>
+        <v>19.4000244140625</v>
       </c>
       <c r="L8">
-        <v>93.68017578125</v>
+        <v>95.259765625</v>
       </c>
       <c r="M8">
-        <v>75</v>
+        <v>72.10009765625</v>
       </c>
       <c r="N8">
-        <v>108.39013671875</v>
+        <v>118.43994140625</v>
       </c>
       <c r="O8">
-        <v>67.83984375</v>
+        <v>70.14013671875</v>
       </c>
       <c r="P8">
-        <v>64.2001953125</v>
+        <v>81.97998046875</v>
       </c>
       <c r="Q8">
-        <v>74.7001953125</v>
+        <v>81.77978515625</v>
       </c>
       <c r="R8">
-        <v>69.6201171875</v>
+        <v>76.31982421875</v>
+      </c>
+      <c r="S8">
+        <v>116.0498046875</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -950,55 +971,58 @@
         <v>26</v>
       </c>
       <c r="B9">
-        <v>61.56005859375</v>
+        <v>56.050048828125</v>
       </c>
       <c r="C9">
-        <v>83.47998046875</v>
+        <v>70.43994140625</v>
       </c>
       <c r="D9">
-        <v>90.4599609375</v>
+        <v>71.64013671875</v>
       </c>
       <c r="E9">
-        <v>76.06005859375</v>
+        <v>56.360107421875</v>
       </c>
       <c r="F9">
-        <v>41.169921875</v>
+        <v>88.240234375</v>
       </c>
       <c r="G9">
-        <v>71.009765625</v>
+        <v>61.989990234375</v>
       </c>
       <c r="H9">
-        <v>65.47021484375</v>
+        <v>48.469970703125</v>
       </c>
       <c r="I9">
-        <v>34.110107421875</v>
+        <v>82.85009765625</v>
       </c>
       <c r="J9">
-        <v>70.740234375</v>
+        <v>85.52978515625</v>
       </c>
       <c r="K9">
-        <v>53.280029296875</v>
+        <v>55.179931640625</v>
       </c>
       <c r="L9">
-        <v>96.4599609375</v>
+        <v>93.68017578125</v>
       </c>
       <c r="M9">
-        <v>64.919921875</v>
+        <v>75</v>
       </c>
       <c r="N9">
-        <v>118.240234375</v>
+        <v>108.39013671875</v>
       </c>
       <c r="O9">
-        <v>58.43994140625</v>
+        <v>67.83984375</v>
       </c>
       <c r="P9">
-        <v>50.199951171875</v>
+        <v>64.2001953125</v>
       </c>
       <c r="Q9">
-        <v>74.5498046875</v>
+        <v>74.7001953125</v>
       </c>
       <c r="R9">
-        <v>82.919921875</v>
+        <v>69.6201171875</v>
+      </c>
+      <c r="S9">
+        <v>104.2998046875</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1006,55 +1030,58 @@
         <v>27</v>
       </c>
       <c r="B10">
-        <v>54.050048828125</v>
+        <v>61.56005859375</v>
       </c>
       <c r="C10">
-        <v>85.7001953125</v>
+        <v>83.47998046875</v>
       </c>
       <c r="D10">
-        <v>65.66015625</v>
+        <v>90.4599609375</v>
       </c>
       <c r="E10">
-        <v>49.449951171875</v>
+        <v>76.06005859375</v>
       </c>
       <c r="F10">
-        <v>87.72021484375</v>
+        <v>41.169921875</v>
       </c>
       <c r="G10">
-        <v>77.7998046875</v>
+        <v>71.009765625</v>
       </c>
       <c r="H10">
-        <v>57.93994140625</v>
+        <v>65.47021484375</v>
       </c>
       <c r="I10">
-        <v>42.89990234375</v>
+        <v>34.110107421875</v>
       </c>
       <c r="J10">
-        <v>97.68017578125</v>
+        <v>70.740234375</v>
       </c>
       <c r="K10">
-        <v>65.3701171875</v>
+        <v>53.280029296875</v>
       </c>
       <c r="L10">
-        <v>82.4599609375</v>
+        <v>96.4599609375</v>
       </c>
       <c r="M10">
-        <v>69.89990234375</v>
+        <v>64.919921875</v>
       </c>
       <c r="N10">
-        <v>108.58984375</v>
+        <v>118.240234375</v>
       </c>
       <c r="O10">
-        <v>71.25</v>
+        <v>58.43994140625</v>
       </c>
       <c r="P10">
-        <v>55.52001953125</v>
+        <v>50.199951171875</v>
       </c>
       <c r="Q10">
-        <v>69.14990234375</v>
+        <v>74.5498046875</v>
       </c>
       <c r="R10">
-        <v>76.6201171875</v>
+        <v>82.919921875</v>
+      </c>
+      <c r="S10">
+        <v>135.0498046875</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1062,55 +1089,58 @@
         <v>28</v>
       </c>
       <c r="B11">
-        <v>55.659912109375</v>
+        <v>54.050048828125</v>
       </c>
       <c r="C11">
-        <v>73.60009765625</v>
+        <v>85.7001953125</v>
       </c>
       <c r="D11">
-        <v>100.06005859375</v>
+        <v>65.66015625</v>
       </c>
       <c r="E11">
-        <v>62.75</v>
+        <v>49.449951171875</v>
       </c>
       <c r="F11">
-        <v>77.22021484375</v>
+        <v>87.72021484375</v>
       </c>
       <c r="G11">
-        <v>88.2099609375</v>
+        <v>77.7998046875</v>
       </c>
       <c r="H11">
-        <v>61.110107421875</v>
+        <v>57.93994140625</v>
       </c>
       <c r="I11">
-        <v>82.81982421875</v>
+        <v>42.89990234375</v>
       </c>
       <c r="J11">
-        <v>85.93994140625</v>
+        <v>97.68017578125</v>
       </c>
       <c r="K11">
-        <v>43.590087890625</v>
+        <v>65.3701171875</v>
       </c>
       <c r="L11">
-        <v>86.9599609375</v>
+        <v>82.4599609375</v>
       </c>
       <c r="M11">
-        <v>101.25</v>
+        <v>69.89990234375</v>
       </c>
       <c r="N11">
-        <v>102.990234375</v>
+        <v>108.58984375</v>
       </c>
       <c r="O11">
-        <v>66.080078125</v>
+        <v>71.25</v>
       </c>
       <c r="P11">
-        <v>49.6201171875</v>
+        <v>55.52001953125</v>
       </c>
       <c r="Q11">
-        <v>76.27978515625</v>
+        <v>69.14990234375</v>
       </c>
       <c r="R11">
-        <v>58.820068359375</v>
+        <v>76.6201171875</v>
+      </c>
+      <c r="S11">
+        <v>125.85009765625</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1118,55 +1148,58 @@
         <v>29</v>
       </c>
       <c r="B12">
-        <v>62.56005859375</v>
+        <v>47.860107421875</v>
       </c>
       <c r="C12">
-        <v>96.47998046875</v>
+        <v>72.18017578125</v>
       </c>
       <c r="D12">
-        <v>87.4599609375</v>
+        <v>97.39990234375</v>
       </c>
       <c r="E12">
-        <v>81.43017578125</v>
+        <v>81.64990234375</v>
       </c>
       <c r="F12">
-        <v>85.669921875</v>
+        <v>84.81982421875</v>
       </c>
       <c r="G12">
-        <v>58.610107421875</v>
+        <v>62.010009765625</v>
       </c>
       <c r="H12">
-        <v>81.56982421875</v>
+        <v>77.06982421875</v>
       </c>
       <c r="I12">
-        <v>73.35009765625</v>
+        <v>80.0498046875</v>
       </c>
       <c r="J12">
-        <v>104.68017578125</v>
+        <v>59.010009765625</v>
       </c>
       <c r="K12">
-        <v>66.89013671875</v>
+        <v>60.169921875</v>
       </c>
       <c r="L12">
-        <v>90.4599609375</v>
+        <v>82.81005859375</v>
       </c>
       <c r="M12">
-        <v>84.39990234375</v>
+        <v>77.35009765625</v>
       </c>
       <c r="N12">
-        <v>108.58984375</v>
+        <v>115.43994140625</v>
       </c>
       <c r="O12">
-        <v>49.280029296875</v>
+        <v>57.72998046875</v>
       </c>
       <c r="P12">
-        <v>54.580078125</v>
+        <v>55.89990234375</v>
       </c>
       <c r="Q12">
-        <v>68.580078125</v>
+        <v>103.39013671875</v>
       </c>
       <c r="R12">
-        <v>70.81982421875</v>
+        <v>60.1201171875</v>
+      </c>
+      <c r="S12">
+        <v>132.9501953125</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1177,52 +1210,55 @@
         <v>55.659912109375</v>
       </c>
       <c r="C13">
-        <v>55.780029296875</v>
+        <v>73.60009765625</v>
       </c>
       <c r="D13">
-        <v>88.93994140625</v>
+        <v>100.06005859375</v>
       </c>
       <c r="E13">
-        <v>59.409912109375</v>
+        <v>62.75</v>
       </c>
       <c r="F13">
-        <v>84.6201171875</v>
+        <v>77.22021484375</v>
       </c>
       <c r="G13">
-        <v>75.81005859375</v>
+        <v>88.2099609375</v>
       </c>
       <c r="H13">
-        <v>83.22021484375</v>
+        <v>61.110107421875</v>
       </c>
       <c r="I13">
-        <v>85.64990234375</v>
+        <v>82.81982421875</v>
       </c>
       <c r="J13">
-        <v>66.93994140625</v>
+        <v>85.93994140625</v>
       </c>
       <c r="K13">
-        <v>58.949951171875</v>
+        <v>43.590087890625</v>
       </c>
       <c r="L13">
-        <v>92.66015625</v>
+        <v>86.9599609375</v>
       </c>
       <c r="M13">
-        <v>76.7998046875</v>
+        <v>101.25</v>
       </c>
       <c r="N13">
-        <v>85.93994140625</v>
+        <v>102.990234375</v>
       </c>
       <c r="O13">
-        <v>66.0498046875</v>
+        <v>66.080078125</v>
       </c>
       <c r="P13">
-        <v>35.419921875</v>
+        <v>49.6201171875</v>
       </c>
       <c r="Q13">
-        <v>91.35009765625</v>
+        <v>76.27978515625</v>
       </c>
       <c r="R13">
-        <v>63.60009765625</v>
+        <v>58.820068359375</v>
+      </c>
+      <c r="S13">
+        <v>111.2001953125</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1230,55 +1266,58 @@
         <v>31</v>
       </c>
       <c r="B14">
-        <v>60.60009765625</v>
+        <v>62.56005859375</v>
       </c>
       <c r="C14">
-        <v>75.8798828125</v>
+        <v>96.47998046875</v>
       </c>
       <c r="D14">
-        <v>87.39013671875</v>
+        <v>87.4599609375</v>
       </c>
       <c r="E14">
-        <v>42.56005859375</v>
+        <v>81.43017578125</v>
       </c>
       <c r="F14">
-        <v>49.77001953125</v>
+        <v>85.669921875</v>
       </c>
       <c r="G14">
-        <v>55.3798828125</v>
+        <v>58.610107421875</v>
       </c>
       <c r="H14">
-        <v>61.8701171875</v>
+        <v>81.56982421875</v>
       </c>
       <c r="I14">
-        <v>70.5400390625</v>
+        <v>73.35009765625</v>
       </c>
       <c r="J14">
-        <v>39.699951171875</v>
+        <v>104.68017578125</v>
       </c>
       <c r="K14">
-        <v>31.75</v>
+        <v>66.89013671875</v>
       </c>
       <c r="L14">
-        <v>51.530029296875</v>
+        <v>90.4599609375</v>
       </c>
       <c r="M14">
-        <v>35.2900390625</v>
+        <v>84.39990234375</v>
       </c>
       <c r="N14">
-        <v>54.830078125</v>
+        <v>108.58984375</v>
       </c>
       <c r="O14">
-        <v>30.030029296875</v>
+        <v>49.280029296875</v>
       </c>
       <c r="P14">
-        <v>42.10009765625</v>
+        <v>54.580078125</v>
       </c>
       <c r="Q14">
-        <v>19.510009765625</v>
+        <v>68.580078125</v>
       </c>
       <c r="R14">
-        <v>52.949951171875</v>
+        <v>70.81982421875</v>
+      </c>
+      <c r="S14">
+        <v>106.10009765625</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1286,391 +1325,412 @@
         <v>32</v>
       </c>
       <c r="B15">
-        <v>61.159912109375</v>
+        <v>55.659912109375</v>
       </c>
       <c r="C15">
-        <v>71.18017578125</v>
+        <v>55.780029296875</v>
       </c>
       <c r="D15">
-        <v>73.06005859375</v>
+        <v>88.93994140625</v>
       </c>
       <c r="E15">
-        <v>42.56005859375</v>
+        <v>59.409912109375</v>
       </c>
       <c r="F15">
-        <v>70.85986328125</v>
+        <v>84.6201171875</v>
       </c>
       <c r="G15">
-        <v>67.58984375</v>
+        <v>75.81005859375</v>
       </c>
       <c r="H15">
-        <v>71.77001953125</v>
+        <v>83.22021484375</v>
       </c>
       <c r="I15">
-        <v>68.25</v>
+        <v>85.64990234375</v>
       </c>
       <c r="J15">
-        <v>80.33984375</v>
+        <v>66.93994140625</v>
       </c>
       <c r="K15">
-        <v>60.050048828125</v>
+        <v>58.949951171875</v>
       </c>
       <c r="L15">
-        <v>89.66015625</v>
+        <v>92.66015625</v>
       </c>
       <c r="M15">
-        <v>81.9501953125</v>
+        <v>76.7998046875</v>
       </c>
       <c r="N15">
-        <v>113.18994140625</v>
+        <v>85.93994140625</v>
       </c>
       <c r="O15">
-        <v>50.75</v>
+        <v>66.0498046875</v>
       </c>
       <c r="P15">
-        <v>45.919921875</v>
+        <v>35.419921875</v>
       </c>
       <c r="Q15">
+        <v>91.35009765625</v>
+      </c>
+      <c r="R15">
         <v>63.60009765625</v>
       </c>
-      <c r="R15">
-        <v>81.9501953125</v>
+      <c r="S15">
+        <v>93.10009765625</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B16">
-        <v>67.16015625</v>
-      </c>
       <c r="C16">
-        <v>86.4501953125</v>
+        <v>95.41015625</v>
       </c>
       <c r="D16">
-        <v>64.35986328125</v>
+        <v>57.0400390625</v>
       </c>
       <c r="E16">
-        <v>61.1298828125</v>
+        <v>72.240234375</v>
       </c>
       <c r="F16">
-        <v>72.759765625</v>
+        <v>69.77001953125</v>
       </c>
       <c r="G16">
-        <v>61.199951171875</v>
+        <v>47.989990234375</v>
       </c>
       <c r="H16">
-        <v>69.60009765625</v>
+        <v>46.550048828125</v>
       </c>
       <c r="I16">
-        <v>67.14990234375</v>
+        <v>59.909912109375</v>
       </c>
       <c r="J16">
-        <v>62.89990234375</v>
+        <v>70.47998046875</v>
       </c>
       <c r="K16">
-        <v>43.25</v>
+        <v>66.580078125</v>
       </c>
       <c r="L16">
-        <v>81.8798828125</v>
+        <v>29.8499755859375</v>
       </c>
       <c r="M16">
-        <v>41.570068359375</v>
+        <v>57.10009765625</v>
       </c>
       <c r="N16">
-        <v>96.83984375</v>
+        <v>31.050048828125</v>
       </c>
       <c r="O16">
-        <v>47.43994140625</v>
+        <v>31.6500244140625</v>
       </c>
       <c r="P16">
-        <v>52.199951171875</v>
+        <v>32.93994140625</v>
       </c>
       <c r="Q16">
-        <v>108.43994140625</v>
+        <v>48.93994140625</v>
       </c>
       <c r="R16">
-        <v>68.22021484375</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18">
+        <v>75.419921875</v>
+      </c>
+      <c r="S16">
+        <v>64.5498046875</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B17">
-        <v>54.89990234375</v>
+        <v>60.60009765625</v>
       </c>
       <c r="C17">
-        <v>77.60009765625</v>
+        <v>75.8798828125</v>
       </c>
       <c r="D17">
-        <v>78.259765625</v>
+        <v>87.39013671875</v>
       </c>
       <c r="E17">
-        <v>45.550048828125</v>
+        <v>42.56005859375</v>
       </c>
       <c r="F17">
-        <v>77.6201171875</v>
+        <v>49.77001953125</v>
       </c>
       <c r="G17">
-        <v>79.009765625</v>
+        <v>55.3798828125</v>
       </c>
       <c r="H17">
-        <v>65.47021484375</v>
+        <v>61.8701171875</v>
       </c>
       <c r="I17">
-        <v>80.85009765625</v>
+        <v>70.5400390625</v>
       </c>
       <c r="J17">
-        <v>94.27978515625</v>
+        <v>39.699951171875</v>
       </c>
       <c r="K17">
-        <v>70.77001953125</v>
+        <v>31.75</v>
       </c>
       <c r="L17">
-        <v>98.56005859375</v>
+        <v>51.530029296875</v>
       </c>
       <c r="M17">
-        <v>83.5</v>
+        <v>35.2900390625</v>
       </c>
       <c r="N17">
-        <v>114.08984375</v>
+        <v>54.830078125</v>
       </c>
       <c r="O17">
-        <v>57.14990234375</v>
+        <v>30.030029296875</v>
       </c>
       <c r="P17">
-        <v>53.929931640625</v>
+        <v>42.10009765625</v>
       </c>
       <c r="Q17">
-        <v>79.2001953125</v>
+        <v>19.510009765625</v>
       </c>
       <c r="R17">
-        <v>66.31982421875</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
+        <v>52.949951171875</v>
+      </c>
+      <c r="S17">
+        <v>55.570068359375</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B18">
-        <v>68.06005859375</v>
+        <v>61.159912109375</v>
       </c>
       <c r="C18">
-        <v>82.18017578125</v>
+        <v>71.18017578125</v>
       </c>
       <c r="D18">
-        <v>105.759765625</v>
+        <v>73.06005859375</v>
       </c>
       <c r="E18">
-        <v>65.14990234375</v>
+        <v>42.56005859375</v>
       </c>
       <c r="F18">
-        <v>93.02001953125</v>
+        <v>70.85986328125</v>
       </c>
       <c r="G18">
-        <v>83</v>
+        <v>67.58984375</v>
       </c>
       <c r="H18">
-        <v>76.97021484375</v>
+        <v>71.77001953125</v>
       </c>
       <c r="I18">
-        <v>76.4501953125</v>
+        <v>68.25</v>
       </c>
       <c r="J18">
-        <v>85.85009765625</v>
+        <v>80.33984375</v>
       </c>
       <c r="K18">
-        <v>58.090087890625</v>
+        <v>60.050048828125</v>
       </c>
       <c r="L18">
-        <v>88.759765625</v>
+        <v>89.66015625</v>
       </c>
       <c r="M18">
-        <v>86.66015625</v>
+        <v>81.9501953125</v>
       </c>
       <c r="N18">
-        <v>106.39013671875</v>
+        <v>113.18994140625</v>
       </c>
       <c r="O18">
-        <v>53.780029296875</v>
+        <v>50.75</v>
       </c>
       <c r="P18">
-        <v>63.75</v>
+        <v>45.919921875</v>
       </c>
       <c r="Q18">
-        <v>73.080078125</v>
+        <v>63.60009765625</v>
       </c>
       <c r="R18">
-        <v>65.6201171875</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18">
+        <v>81.9501953125</v>
+      </c>
+      <c r="S18">
+        <v>132.1201171875</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19">
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B19">
-        <v>53.659912109375</v>
+        <v>67.16015625</v>
       </c>
       <c r="C19">
-        <v>81.47998046875</v>
+        <v>86.4501953125</v>
       </c>
       <c r="D19">
-        <v>79.259765625</v>
+        <v>64.35986328125</v>
       </c>
       <c r="E19">
-        <v>86.43017578125</v>
+        <v>61.1298828125</v>
       </c>
       <c r="F19">
-        <v>86.419921875</v>
+        <v>72.759765625</v>
       </c>
       <c r="G19">
-        <v>47.389892578125</v>
+        <v>61.199951171875</v>
       </c>
       <c r="H19">
-        <v>67.27001953125</v>
+        <v>69.60009765625</v>
       </c>
       <c r="I19">
-        <v>75.75</v>
+        <v>67.14990234375</v>
       </c>
       <c r="J19">
-        <v>85.9599609375</v>
+        <v>62.89990234375</v>
       </c>
       <c r="K19">
-        <v>39.469970703125</v>
+        <v>43.25</v>
       </c>
       <c r="L19">
-        <v>85.16015625</v>
+        <v>81.8798828125</v>
       </c>
       <c r="M19">
-        <v>81.4501953125</v>
+        <v>41.570068359375</v>
       </c>
       <c r="N19">
-        <v>113.2900390625</v>
+        <v>96.83984375</v>
       </c>
       <c r="O19">
-        <v>61.949951171875</v>
+        <v>47.43994140625</v>
       </c>
       <c r="P19">
-        <v>60.169921875</v>
+        <v>52.199951171875</v>
       </c>
       <c r="Q19">
-        <v>72.27978515625</v>
+        <v>108.43994140625</v>
       </c>
       <c r="R19">
-        <v>65.31982421875</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
+        <v>68.22021484375</v>
+      </c>
+      <c r="S19">
+        <v>99.2998046875</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B20">
-        <v>47.860107421875</v>
+        <v>54.89990234375</v>
       </c>
       <c r="C20">
-        <v>72.18017578125</v>
+        <v>77.60009765625</v>
       </c>
       <c r="D20">
-        <v>97.39990234375</v>
+        <v>78.259765625</v>
       </c>
       <c r="E20">
-        <v>81.64990234375</v>
+        <v>45.550048828125</v>
       </c>
       <c r="F20">
-        <v>84.81982421875</v>
+        <v>77.6201171875</v>
       </c>
       <c r="G20">
-        <v>62.010009765625</v>
+        <v>79.009765625</v>
       </c>
       <c r="H20">
-        <v>77.06982421875</v>
+        <v>65.47021484375</v>
       </c>
       <c r="I20">
-        <v>80.0498046875</v>
+        <v>80.85009765625</v>
       </c>
       <c r="J20">
-        <v>59.010009765625</v>
+        <v>94.27978515625</v>
       </c>
       <c r="K20">
-        <v>60.169921875</v>
+        <v>70.77001953125</v>
       </c>
       <c r="L20">
-        <v>82.81005859375</v>
+        <v>98.56005859375</v>
       </c>
       <c r="M20">
-        <v>77.35009765625</v>
+        <v>83.5</v>
       </c>
       <c r="N20">
-        <v>115.43994140625</v>
+        <v>114.08984375</v>
       </c>
       <c r="O20">
-        <v>57.72998046875</v>
+        <v>57.14990234375</v>
       </c>
       <c r="P20">
-        <v>55.89990234375</v>
+        <v>53.929931640625</v>
       </c>
       <c r="Q20">
-        <v>103.39013671875</v>
+        <v>79.2001953125</v>
       </c>
       <c r="R20">
-        <v>60.1201171875</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18">
+        <v>66.31982421875</v>
+      </c>
+      <c r="S20">
+        <v>110.0498046875</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" s="1" t="s">
         <v>38</v>
       </c>
+      <c r="B21">
+        <v>68.06005859375</v>
+      </c>
       <c r="C21">
-        <v>95.41015625</v>
+        <v>82.18017578125</v>
       </c>
       <c r="D21">
-        <v>57.0400390625</v>
+        <v>105.759765625</v>
       </c>
       <c r="E21">
-        <v>72.240234375</v>
+        <v>65.14990234375</v>
       </c>
       <c r="F21">
-        <v>69.77001953125</v>
+        <v>93.02001953125</v>
       </c>
       <c r="G21">
-        <v>47.989990234375</v>
+        <v>83</v>
       </c>
       <c r="H21">
-        <v>46.550048828125</v>
+        <v>76.97021484375</v>
       </c>
       <c r="I21">
-        <v>59.909912109375</v>
+        <v>76.4501953125</v>
       </c>
       <c r="J21">
-        <v>70.47998046875</v>
+        <v>85.85009765625</v>
       </c>
       <c r="K21">
-        <v>66.580078125</v>
+        <v>58.090087890625</v>
       </c>
       <c r="L21">
-        <v>29.8499755859375</v>
+        <v>88.759765625</v>
       </c>
       <c r="M21">
-        <v>57.10009765625</v>
+        <v>86.66015625</v>
       </c>
       <c r="N21">
-        <v>31.050048828125</v>
+        <v>106.39013671875</v>
       </c>
       <c r="O21">
-        <v>31.6500244140625</v>
+        <v>53.780029296875</v>
       </c>
       <c r="P21">
-        <v>32.93994140625</v>
+        <v>63.75</v>
       </c>
       <c r="Q21">
-        <v>48.93994140625</v>
+        <v>73.080078125</v>
       </c>
       <c r="R21">
-        <v>75.419921875</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18">
+        <v>65.6201171875</v>
+      </c>
+      <c r="S21">
+        <v>111.64990234375</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1690,40 +1750,43 @@
         <v>23</v>
       </c>
       <c r="G22" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H22" t="s">
         <v>23</v>
       </c>
       <c r="I22" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J22" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K22" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L22" t="s">
         <v>19</v>
       </c>
       <c r="M22" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O22" t="s">
         <v>21</v>
       </c>
       <c r="P22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="R22" t="s">
         <v>21</v>
+      </c>
+      <c r="S22" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
